--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129306536</v>
+        <v>129309881</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451170</v>
+        <v>451386</v>
       </c>
       <c r="R2" t="n">
-        <v>6752562</v>
+        <v>6752391</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129309881</v>
+        <v>129316313</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451386</v>
+        <v>451213</v>
       </c>
       <c r="R3" t="n">
-        <v>6752391</v>
+        <v>6752316</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,11 +868,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129316313</v>
+        <v>129306536</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451213</v>
+        <v>451170</v>
       </c>
       <c r="R4" t="n">
-        <v>6752316</v>
+        <v>6752562</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,52 +1001,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129313901</v>
+        <v>129307645</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451299</v>
+        <v>451237</v>
       </c>
       <c r="R5" t="n">
-        <v>6752289</v>
+        <v>6752478</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,12 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129313806</v>
+        <v>129307362</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451299</v>
+        <v>451244</v>
       </c>
       <c r="R6" t="n">
-        <v>6752289</v>
+        <v>6752466</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1197,12 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bild på gran, garn</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,7 +1223,7 @@
         <v>129306875</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1330,7 @@
         <v>129306675</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1555,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129307645</v>
+        <v>129307805</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,37 +1557,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451237</v>
+        <v>451335</v>
       </c>
       <c r="R10" t="n">
-        <v>6752478</v>
+        <v>6752504</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1636,11 +1632,6 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129307362</v>
+        <v>129307040</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,37 +1669,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451244</v>
+        <v>451262</v>
       </c>
       <c r="R11" t="n">
-        <v>6752466</v>
+        <v>6752514</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129312692</v>
+        <v>129306575</v>
       </c>
       <c r="B12" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451369</v>
+        <v>451153</v>
       </c>
       <c r="R12" t="n">
-        <v>6752313</v>
+        <v>6752545</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1840,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1850,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129306575</v>
+        <v>129312692</v>
       </c>
       <c r="B13" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451153</v>
+        <v>451369</v>
       </c>
       <c r="R13" t="n">
-        <v>6752545</v>
+        <v>6752313</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1961,7 +1957,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,10 +1984,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129307040</v>
+        <v>129307114</v>
       </c>
       <c r="B14" t="n">
-        <v>57722</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,27 +1995,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2100,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129307805</v>
+        <v>129314017</v>
       </c>
       <c r="B15" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,39 +2107,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451335</v>
+        <v>451253</v>
       </c>
       <c r="R15" t="n">
-        <v>6752504</v>
+        <v>6752304</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2185,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129307114</v>
+        <v>129306457</v>
       </c>
       <c r="B16" t="n">
-        <v>57885</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,42 +2214,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451262</v>
+        <v>451149</v>
       </c>
       <c r="R16" t="n">
-        <v>6752514</v>
+        <v>6752603</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2324,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129314017</v>
+        <v>129306554</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451253</v>
+        <v>451170</v>
       </c>
       <c r="R17" t="n">
-        <v>6752304</v>
+        <v>6752562</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2404,7 +2390,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129306457</v>
+        <v>129306100</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451149</v>
+        <v>451093</v>
       </c>
       <c r="R18" t="n">
-        <v>6752603</v>
+        <v>6752490</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2538,32 +2524,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129306554</v>
+        <v>129307042</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2573,13 +2559,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451170</v>
+        <v>451262</v>
       </c>
       <c r="R19" t="n">
-        <v>6752562</v>
+        <v>6752514</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2645,32 +2631,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129307042</v>
+        <v>129306511</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2680,13 +2666,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451262</v>
+        <v>451170</v>
       </c>
       <c r="R20" t="n">
-        <v>6752514</v>
+        <v>6752562</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2752,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129306100</v>
+        <v>129308438</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2763,34 +2749,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451093</v>
+        <v>451260</v>
       </c>
       <c r="R21" t="n">
-        <v>6752490</v>
+        <v>6752424</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2859,32 +2850,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129306511</v>
+        <v>129306556</v>
       </c>
       <c r="B22" t="n">
-        <v>79658</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2894,10 +2885,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451170</v>
+        <v>451153</v>
       </c>
       <c r="R22" t="n">
-        <v>6752562</v>
+        <v>6752545</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2966,32 +2957,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129306556</v>
+        <v>129308406</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79631</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3001,10 +2992,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451153</v>
+        <v>451275</v>
       </c>
       <c r="R23" t="n">
-        <v>6752545</v>
+        <v>6752429</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3073,10 +3064,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129308438</v>
+        <v>129311305</v>
       </c>
       <c r="B24" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3084,42 +3075,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451260</v>
+        <v>451358</v>
       </c>
       <c r="R24" t="n">
         <v>6752424</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3148,7 +3134,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3158,7 +3144,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3185,10 +3176,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129311305</v>
+        <v>129307012</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3220,10 +3211,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451358</v>
+        <v>451262</v>
       </c>
       <c r="R25" t="n">
-        <v>6752424</v>
+        <v>6752514</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3255,7 +3246,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3265,7 +3256,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3297,10 +3288,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129308406</v>
+        <v>129307237</v>
       </c>
       <c r="B26" t="n">
-        <v>79629</v>
+        <v>57724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3308,34 +3299,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451275</v>
+        <v>451256</v>
       </c>
       <c r="R26" t="n">
-        <v>6752429</v>
+        <v>6752469</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3404,10 +3400,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129307237</v>
+        <v>129306315</v>
       </c>
       <c r="B27" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3415,39 +3411,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>451256</v>
+        <v>451102</v>
       </c>
       <c r="R27" t="n">
-        <v>6752469</v>
+        <v>6752519</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,32 +3507,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129307012</v>
+        <v>129310109</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3551,13 +3542,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>451262</v>
+        <v>451435</v>
       </c>
       <c r="R28" t="n">
-        <v>6752514</v>
+        <v>6752354</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3586,7 +3577,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3596,12 +3587,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3628,10 +3614,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129306315</v>
+        <v>129308422</v>
       </c>
       <c r="B29" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>451102</v>
+        <v>451275</v>
       </c>
       <c r="R29" t="n">
-        <v>6752519</v>
+        <v>6752429</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3735,32 +3721,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310109</v>
+        <v>129306588</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3770,10 +3756,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>451435</v>
+        <v>451153</v>
       </c>
       <c r="R30" t="n">
-        <v>6752354</v>
+        <v>6752545</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3805,7 +3791,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3801,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,10 +3828,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129314054</v>
+        <v>129306615</v>
       </c>
       <c r="B31" t="n">
-        <v>78797</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,21 +3839,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3877,10 +3863,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>451213</v>
+        <v>451164</v>
       </c>
       <c r="R31" t="n">
-        <v>6752316</v>
+        <v>6752537</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,7 +3898,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3922,7 +3908,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3952,7 +3938,7 @@
         <v>129313973</v>
       </c>
       <c r="B32" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4056,10 +4042,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129306588</v>
+        <v>129314054</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>78799</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4067,21 +4053,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4091,10 +4077,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>451153</v>
+        <v>451213</v>
       </c>
       <c r="R33" t="n">
-        <v>6752545</v>
+        <v>6752316</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4126,7 +4112,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4136,7 +4122,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4163,10 +4149,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129306615</v>
+        <v>129311235</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4198,10 +4184,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451164</v>
+        <v>451357</v>
       </c>
       <c r="R34" t="n">
-        <v>6752537</v>
+        <v>6752476</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4233,7 +4219,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4243,7 +4229,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4270,10 +4256,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129308422</v>
+        <v>129310178</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>78444</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4281,21 +4267,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4305,10 +4291,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451275</v>
+        <v>451435</v>
       </c>
       <c r="R35" t="n">
-        <v>6752429</v>
+        <v>6752354</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4340,7 +4326,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4350,7 +4336,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4377,10 +4363,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129311235</v>
+        <v>129307777</v>
       </c>
       <c r="B36" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4388,21 +4374,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4412,13 +4398,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451357</v>
+        <v>451291</v>
       </c>
       <c r="R36" t="n">
-        <v>6752476</v>
+        <v>6752489</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4447,7 +4433,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4457,7 +4443,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4484,32 +4470,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129310178</v>
+        <v>129309657</v>
       </c>
       <c r="B37" t="n">
-        <v>78442</v>
+        <v>92835</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4519,10 +4505,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451435</v>
+        <v>451370</v>
       </c>
       <c r="R37" t="n">
-        <v>6752354</v>
+        <v>6752389</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4594,7 +4580,7 @@
         <v>129310404</v>
       </c>
       <c r="B38" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4698,32 +4684,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129309657</v>
+        <v>129307775</v>
       </c>
       <c r="B39" t="n">
-        <v>92833</v>
+        <v>79631</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4733,13 +4719,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>451370</v>
+        <v>451291</v>
       </c>
       <c r="R39" t="n">
-        <v>6752389</v>
+        <v>6752489</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4768,7 +4754,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4778,7 +4764,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4805,10 +4791,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129307777</v>
+        <v>129306610</v>
       </c>
       <c r="B40" t="n">
-        <v>79658</v>
+        <v>79631</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4816,21 +4802,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4840,13 +4826,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>451291</v>
+        <v>451164</v>
       </c>
       <c r="R40" t="n">
-        <v>6752489</v>
+        <v>6752537</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4912,10 +4898,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129307775</v>
+        <v>129307878</v>
       </c>
       <c r="B41" t="n">
-        <v>79629</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4923,21 +4909,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4947,10 +4933,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451291</v>
+        <v>451297</v>
       </c>
       <c r="R41" t="n">
-        <v>6752489</v>
+        <v>6752466</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -4993,6 +4979,11 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5019,10 +5010,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129306610</v>
+        <v>129313715</v>
       </c>
       <c r="B42" t="n">
-        <v>79629</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,21 +5021,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5054,10 +5045,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451164</v>
+        <v>451335</v>
       </c>
       <c r="R42" t="n">
-        <v>6752537</v>
+        <v>6752312</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5089,7 +5080,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5099,7 +5090,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,10 +5117,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129313715</v>
+        <v>129310209</v>
       </c>
       <c r="B43" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5161,10 +5152,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>451335</v>
+        <v>451435</v>
       </c>
       <c r="R43" t="n">
-        <v>6752312</v>
+        <v>6752354</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5207,6 +5198,11 @@
       <c r="AB43" t="inlineStr">
         <is>
           <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5233,10 +5229,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129310209</v>
+        <v>129310740</v>
       </c>
       <c r="B44" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5244,21 +5240,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5268,10 +5264,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>451435</v>
+        <v>451416</v>
       </c>
       <c r="R44" t="n">
-        <v>6752354</v>
+        <v>6752417</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5314,11 +5310,6 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5345,10 +5336,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129307878</v>
+        <v>129306322</v>
       </c>
       <c r="B45" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5380,13 +5371,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>451297</v>
+        <v>451096</v>
       </c>
       <c r="R45" t="n">
-        <v>6752466</v>
+        <v>6752528</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5426,11 +5417,6 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5457,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129310740</v>
+        <v>129306645</v>
       </c>
       <c r="B46" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5492,10 +5478,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451416</v>
+        <v>451189</v>
       </c>
       <c r="R46" t="n">
-        <v>6752417</v>
+        <v>6752531</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5527,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5537,7 +5523,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5564,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129306322</v>
+        <v>129310637</v>
       </c>
       <c r="B47" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5599,10 +5585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451096</v>
+        <v>451442</v>
       </c>
       <c r="R47" t="n">
-        <v>6752528</v>
+        <v>6752403</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5634,7 +5620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5644,7 +5630,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5671,10 +5662,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129306645</v>
+        <v>129310466</v>
       </c>
       <c r="B48" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5706,10 +5697,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451189</v>
+        <v>451463</v>
       </c>
       <c r="R48" t="n">
-        <v>6752531</v>
+        <v>6752384</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5741,7 +5732,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5751,7 +5742,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5778,10 +5769,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129310637</v>
+        <v>129307334</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5789,34 +5780,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>451442</v>
+        <v>451244</v>
       </c>
       <c r="R49" t="n">
-        <v>6752403</v>
+        <v>6752466</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5848,7 +5844,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5858,12 +5854,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5890,32 +5881,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129310466</v>
+        <v>129307338</v>
       </c>
       <c r="B50" t="n">
-        <v>79658</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5925,10 +5916,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451463</v>
+        <v>451244</v>
       </c>
       <c r="R50" t="n">
-        <v>6752384</v>
+        <v>6752466</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5960,7 +5951,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5970,7 +5961,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5997,45 +5988,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129307338</v>
+        <v>129306533</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451244</v>
+        <v>451170</v>
       </c>
       <c r="R51" t="n">
-        <v>6752466</v>
+        <v>6752562</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6104,50 +6100,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129307334</v>
+        <v>129307240</v>
       </c>
       <c r="B52" t="n">
-        <v>57722</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451244</v>
+        <v>451256</v>
       </c>
       <c r="R52" t="n">
-        <v>6752466</v>
+        <v>6752469</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6216,32 +6207,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129307240</v>
+        <v>129308051</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6251,13 +6242,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451256</v>
+        <v>451352</v>
       </c>
       <c r="R53" t="n">
-        <v>6752469</v>
+        <v>6752454</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6297,6 +6288,11 @@
       <c r="AB53" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6323,10 +6319,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129306533</v>
+        <v>129307728</v>
       </c>
       <c r="B54" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6334,42 +6330,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451170</v>
+        <v>451291</v>
       </c>
       <c r="R54" t="n">
-        <v>6752562</v>
+        <v>6752489</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6409,6 +6400,11 @@
       <c r="AB54" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6435,10 +6431,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129308051</v>
+        <v>129308409</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6446,21 +6442,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6470,13 +6466,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451352</v>
+        <v>451275</v>
       </c>
       <c r="R55" t="n">
-        <v>6752454</v>
+        <v>6752429</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6516,11 +6512,6 @@
       <c r="AB55" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6547,10 +6538,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129307728</v>
+        <v>129307246</v>
       </c>
       <c r="B56" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6582,13 +6573,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451291</v>
+        <v>451256</v>
       </c>
       <c r="R56" t="n">
-        <v>6752489</v>
+        <v>6752469</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6628,11 +6619,6 @@
       <c r="AB56" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6659,10 +6645,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129308409</v>
+        <v>129310742</v>
       </c>
       <c r="B57" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6670,21 +6656,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6694,10 +6680,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451275</v>
+        <v>451416</v>
       </c>
       <c r="R57" t="n">
-        <v>6752429</v>
+        <v>6752417</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6729,7 +6715,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6739,7 +6725,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6769,7 +6755,7 @@
         <v>129306555</v>
       </c>
       <c r="B58" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6878,10 +6864,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129307246</v>
+        <v>129309688</v>
       </c>
       <c r="B59" t="n">
-        <v>79039</v>
+        <v>79631</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6889,21 +6875,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6913,10 +6899,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451256</v>
+        <v>451370</v>
       </c>
       <c r="R59" t="n">
-        <v>6752469</v>
+        <v>6752389</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6948,7 +6934,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6958,7 +6944,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6985,10 +6971,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129309688</v>
+        <v>129310867</v>
       </c>
       <c r="B60" t="n">
-        <v>79629</v>
+        <v>79041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6996,21 +6982,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7020,10 +7006,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>451370</v>
+        <v>451426</v>
       </c>
       <c r="R60" t="n">
-        <v>6752389</v>
+        <v>6752417</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7066,6 +7052,11 @@
       <c r="AB60" t="inlineStr">
         <is>
           <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Nära sälg</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7092,45 +7083,49 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129310742</v>
+        <v>129313901</v>
       </c>
       <c r="B61" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>451416</v>
+        <v>451299</v>
       </c>
       <c r="R61" t="n">
-        <v>6752417</v>
+        <v>6752289</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7173,6 +7168,11 @@
       <c r="AB61" t="inlineStr">
         <is>
           <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7199,10 +7199,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129310867</v>
+        <v>129313806</v>
       </c>
       <c r="B62" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7234,10 +7234,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>451426</v>
+        <v>451299</v>
       </c>
       <c r="R62" t="n">
-        <v>6752417</v>
+        <v>6752289</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Nära sälg</t>
+          <t>Bild på gran, garn</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7308,6 +7308,228 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129322141</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Sundsmor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>451065</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6752410</v>
+      </c>
+      <c r="S63" t="n">
+        <v>50</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter Högstubben på de två sista bilderna ligger strax utanför anmälan där garnlaven noterats</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129309515</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91506</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Sundsmor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>451370</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6752389</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Vedsvampar på granlåga</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129309881</v>
+        <v>129306536</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451386</v>
+        <v>451170</v>
       </c>
       <c r="R2" t="n">
-        <v>6752391</v>
+        <v>6752562</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129316313</v>
+        <v>129309881</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -822,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451213</v>
+        <v>451386</v>
       </c>
       <c r="R3" t="n">
-        <v>6752316</v>
+        <v>6752391</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,6 +863,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129306536</v>
+        <v>129316313</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451170</v>
+        <v>451213</v>
       </c>
       <c r="R4" t="n">
-        <v>6752562</v>
+        <v>6752316</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129307645</v>
+        <v>129306869</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451237</v>
+        <v>451243</v>
       </c>
       <c r="R5" t="n">
-        <v>6752478</v>
+        <v>6752517</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,11 +1082,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129307362</v>
+        <v>129307645</v>
       </c>
       <c r="B6" t="n">
         <v>79041</v>
@@ -1148,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451244</v>
+        <v>451237</v>
       </c>
       <c r="R6" t="n">
-        <v>6752466</v>
+        <v>6752478</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,6 +1189,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129306875</v>
+        <v>129307362</v>
       </c>
       <c r="B7" t="n">
         <v>79041</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451243</v>
+        <v>451244</v>
       </c>
       <c r="R7" t="n">
-        <v>6752517</v>
+        <v>6752466</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129306675</v>
+        <v>129306875</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451206</v>
+        <v>451243</v>
       </c>
       <c r="R8" t="n">
-        <v>6752540</v>
+        <v>6752517</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1408,11 +1408,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129306869</v>
+        <v>129306675</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,13 +1469,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451243</v>
+        <v>451206</v>
       </c>
       <c r="R9" t="n">
-        <v>6752517</v>
+        <v>6752540</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1520,6 +1515,11 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2738,50 +2738,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129308438</v>
+        <v>129306556</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451260</v>
+        <v>451153</v>
       </c>
       <c r="R21" t="n">
-        <v>6752424</v>
+        <v>6752545</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2850,45 +2845,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129306556</v>
+        <v>129308438</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451153</v>
+        <v>451260</v>
       </c>
       <c r="R22" t="n">
-        <v>6752545</v>
+        <v>6752424</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2957,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129308406</v>
+        <v>129307237</v>
       </c>
       <c r="B23" t="n">
-        <v>79631</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,34 +2968,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451275</v>
+        <v>451256</v>
       </c>
       <c r="R23" t="n">
-        <v>6752429</v>
+        <v>6752469</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3288,10 +3293,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129307237</v>
+        <v>129308406</v>
       </c>
       <c r="B26" t="n">
-        <v>57724</v>
+        <v>79631</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3299,39 +3304,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451256</v>
+        <v>451275</v>
       </c>
       <c r="R26" t="n">
-        <v>6752469</v>
+        <v>6752429</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4149,32 +4149,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129311235</v>
+        <v>129309657</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>92835</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451357</v>
+        <v>451370</v>
       </c>
       <c r="R34" t="n">
-        <v>6752476</v>
+        <v>6752389</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129310178</v>
+        <v>129311235</v>
       </c>
       <c r="B35" t="n">
-        <v>78444</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451435</v>
+        <v>451357</v>
       </c>
       <c r="R35" t="n">
-        <v>6752354</v>
+        <v>6752476</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4363,10 +4363,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129307777</v>
+        <v>129310178</v>
       </c>
       <c r="B36" t="n">
-        <v>79660</v>
+        <v>78444</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4374,21 +4374,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451291</v>
+        <v>451435</v>
       </c>
       <c r="R36" t="n">
-        <v>6752489</v>
+        <v>6752354</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,32 +4470,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129309657</v>
+        <v>129307777</v>
       </c>
       <c r="B37" t="n">
-        <v>92835</v>
+        <v>79660</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451370</v>
+        <v>451291</v>
       </c>
       <c r="R37" t="n">
-        <v>6752389</v>
+        <v>6752489</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5988,50 +5988,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129306533</v>
+        <v>129307240</v>
       </c>
       <c r="B51" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451170</v>
+        <v>451256</v>
       </c>
       <c r="R51" t="n">
-        <v>6752562</v>
+        <v>6752469</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6100,45 +6095,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129307240</v>
+        <v>129306533</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451256</v>
+        <v>451170</v>
       </c>
       <c r="R52" t="n">
-        <v>6752469</v>
+        <v>6752562</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129307805</v>
+        <v>129306575</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,39 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451335</v>
+        <v>451153</v>
       </c>
       <c r="R10" t="n">
-        <v>6752504</v>
+        <v>6752545</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129307040</v>
+        <v>129312692</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,42 +1664,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451262</v>
+        <v>451369</v>
       </c>
       <c r="R11" t="n">
-        <v>6752514</v>
+        <v>6752313</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129306575</v>
+        <v>129307805</v>
       </c>
       <c r="B12" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,34 +1771,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451153</v>
+        <v>451335</v>
       </c>
       <c r="R12" t="n">
-        <v>6752545</v>
+        <v>6752504</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129312692</v>
+        <v>129307040</v>
       </c>
       <c r="B13" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,37 +1883,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451369</v>
+        <v>451262</v>
       </c>
       <c r="R13" t="n">
-        <v>6752313</v>
+        <v>6752514</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2631,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129306511</v>
+        <v>129308438</v>
       </c>
       <c r="B20" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,34 +2642,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451170</v>
+        <v>451260</v>
       </c>
       <c r="R20" t="n">
-        <v>6752562</v>
+        <v>6752424</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,32 +2743,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129306556</v>
+        <v>129306511</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2773,10 +2778,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451153</v>
+        <v>451170</v>
       </c>
       <c r="R21" t="n">
-        <v>6752545</v>
+        <v>6752562</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2845,50 +2850,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129308438</v>
+        <v>129306556</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451260</v>
+        <v>451153</v>
       </c>
       <c r="R22" t="n">
-        <v>6752424</v>
+        <v>6752545</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2957,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129307237</v>
+        <v>129311305</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,42 +2968,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451256</v>
+        <v>451358</v>
       </c>
       <c r="R23" t="n">
-        <v>6752469</v>
+        <v>6752424</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3032,7 +3027,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3042,7 +3037,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,7 +3069,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129311305</v>
+        <v>129307012</v>
       </c>
       <c r="B24" t="n">
         <v>79041</v>
@@ -3104,10 +3104,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451358</v>
+        <v>451262</v>
       </c>
       <c r="R24" t="n">
-        <v>6752424</v>
+        <v>6752514</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3181,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129307012</v>
+        <v>129308406</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,21 +3192,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3216,13 +3216,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451262</v>
+        <v>451275</v>
       </c>
       <c r="R25" t="n">
-        <v>6752514</v>
+        <v>6752429</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3262,11 +3262,6 @@
       <c r="AB25" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3293,10 +3288,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129308406</v>
+        <v>129307237</v>
       </c>
       <c r="B26" t="n">
-        <v>79631</v>
+        <v>57724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3304,34 +3299,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451275</v>
+        <v>451256</v>
       </c>
       <c r="R26" t="n">
-        <v>6752429</v>
+        <v>6752469</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -5988,32 +5988,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129307240</v>
+        <v>129308051</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6023,13 +6023,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451256</v>
+        <v>451352</v>
       </c>
       <c r="R51" t="n">
-        <v>6752469</v>
+        <v>6752454</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6069,6 +6069,11 @@
       <c r="AB51" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6095,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129306533</v>
+        <v>129307728</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6106,42 +6111,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451170</v>
+        <v>451291</v>
       </c>
       <c r="R52" t="n">
-        <v>6752562</v>
+        <v>6752489</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6181,6 +6181,11 @@
       <c r="AB52" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6207,10 +6212,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129308051</v>
+        <v>129308409</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6218,21 +6223,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6242,13 +6247,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451352</v>
+        <v>451275</v>
       </c>
       <c r="R53" t="n">
-        <v>6752454</v>
+        <v>6752429</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6288,11 +6293,6 @@
       <c r="AB53" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6319,32 +6319,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129307728</v>
+        <v>129307240</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6354,13 +6354,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451291</v>
+        <v>451256</v>
       </c>
       <c r="R54" t="n">
-        <v>6752489</v>
+        <v>6752469</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6400,11 +6400,6 @@
       <c r="AB54" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6431,10 +6426,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129308409</v>
+        <v>129306533</v>
       </c>
       <c r="B55" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6442,34 +6437,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451275</v>
+        <v>451170</v>
       </c>
       <c r="R55" t="n">
-        <v>6752429</v>
+        <v>6752562</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129306536</v>
+        <v>129309881</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451170</v>
+        <v>451386</v>
       </c>
       <c r="R2" t="n">
-        <v>6752562</v>
+        <v>6752391</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129309881</v>
+        <v>129316313</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -817,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451386</v>
+        <v>451213</v>
       </c>
       <c r="R3" t="n">
-        <v>6752391</v>
+        <v>6752316</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,11 +868,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129316313</v>
+        <v>129306536</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451213</v>
+        <v>451170</v>
       </c>
       <c r="R4" t="n">
-        <v>6752316</v>
+        <v>6752562</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129306869</v>
+        <v>129307645</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451243</v>
+        <v>451237</v>
       </c>
       <c r="R5" t="n">
-        <v>6752517</v>
+        <v>6752478</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,6 +1082,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129307645</v>
+        <v>129307362</v>
       </c>
       <c r="B6" t="n">
         <v>79041</v>
@@ -1143,13 +1148,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451237</v>
+        <v>451244</v>
       </c>
       <c r="R6" t="n">
-        <v>6752478</v>
+        <v>6752466</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,11 +1194,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129307362</v>
+        <v>129306875</v>
       </c>
       <c r="B7" t="n">
         <v>79041</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451244</v>
+        <v>451243</v>
       </c>
       <c r="R7" t="n">
-        <v>6752466</v>
+        <v>6752517</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129306875</v>
+        <v>129306675</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451243</v>
+        <v>451206</v>
       </c>
       <c r="R8" t="n">
-        <v>6752517</v>
+        <v>6752540</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1408,6 +1408,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,32 +1439,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129306675</v>
+        <v>129306869</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,13 +1474,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451206</v>
+        <v>451243</v>
       </c>
       <c r="R9" t="n">
-        <v>6752540</v>
+        <v>6752517</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1515,11 +1520,6 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129306575</v>
+        <v>129307040</v>
       </c>
       <c r="B10" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,37 +1557,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451153</v>
+        <v>451262</v>
       </c>
       <c r="R10" t="n">
-        <v>6752545</v>
+        <v>6752514</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1653,7 +1658,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129312692</v>
+        <v>129306575</v>
       </c>
       <c r="B11" t="n">
         <v>79660</v>
@@ -1688,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451369</v>
+        <v>451153</v>
       </c>
       <c r="R11" t="n">
-        <v>6752313</v>
+        <v>6752545</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129307805</v>
+        <v>129312692</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,39 +1776,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451335</v>
+        <v>451369</v>
       </c>
       <c r="R12" t="n">
-        <v>6752504</v>
+        <v>6752313</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,7 +1872,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129307040</v>
+        <v>129307805</v>
       </c>
       <c r="B13" t="n">
         <v>57724</v>
@@ -1903,7 +1903,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451262</v>
+        <v>451335</v>
       </c>
       <c r="R13" t="n">
-        <v>6752514</v>
+        <v>6752504</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2631,50 +2631,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129308438</v>
+        <v>129306556</v>
       </c>
       <c r="B20" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451260</v>
+        <v>451153</v>
       </c>
       <c r="R20" t="n">
-        <v>6752424</v>
+        <v>6752545</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2743,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129306511</v>
+        <v>129308438</v>
       </c>
       <c r="B21" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2754,34 +2749,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451170</v>
+        <v>451260</v>
       </c>
       <c r="R21" t="n">
-        <v>6752562</v>
+        <v>6752424</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2850,32 +2850,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129306556</v>
+        <v>129306511</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451153</v>
+        <v>451170</v>
       </c>
       <c r="R22" t="n">
-        <v>6752545</v>
+        <v>6752562</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3181,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129308406</v>
+        <v>129307237</v>
       </c>
       <c r="B25" t="n">
-        <v>79631</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,34 +3192,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451275</v>
+        <v>451256</v>
       </c>
       <c r="R25" t="n">
-        <v>6752429</v>
+        <v>6752469</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3288,10 +3293,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129307237</v>
+        <v>129308406</v>
       </c>
       <c r="B26" t="n">
-        <v>57724</v>
+        <v>79631</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3299,39 +3304,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451256</v>
+        <v>451275</v>
       </c>
       <c r="R26" t="n">
-        <v>6752469</v>
+        <v>6752429</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4152,7 +4152,7 @@
         <v>129309657</v>
       </c>
       <c r="B34" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5662,10 +5662,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129310466</v>
+        <v>129307334</v>
       </c>
       <c r="B48" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5673,34 +5673,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451463</v>
+        <v>451244</v>
       </c>
       <c r="R48" t="n">
-        <v>6752384</v>
+        <v>6752466</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5732,7 +5737,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5742,7 +5747,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5769,10 +5774,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129307334</v>
+        <v>129310466</v>
       </c>
       <c r="B49" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5780,39 +5785,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>451244</v>
+        <v>451463</v>
       </c>
       <c r="R49" t="n">
-        <v>6752466</v>
+        <v>6752384</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6319,45 +6319,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129307240</v>
+        <v>129306533</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451256</v>
+        <v>451170</v>
       </c>
       <c r="R54" t="n">
-        <v>6752469</v>
+        <v>6752562</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6426,50 +6431,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129306533</v>
+        <v>129307240</v>
       </c>
       <c r="B55" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451170</v>
+        <v>451256</v>
       </c>
       <c r="R55" t="n">
-        <v>6752562</v>
+        <v>6752469</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6752,10 +6752,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129306555</v>
+        <v>129309688</v>
       </c>
       <c r="B58" t="n">
-        <v>57724</v>
+        <v>79631</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6763,39 +6763,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451153</v>
+        <v>451370</v>
       </c>
       <c r="R58" t="n">
-        <v>6752545</v>
+        <v>6752389</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6827,7 +6822,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6837,7 +6832,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6864,10 +6859,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129309688</v>
+        <v>129306555</v>
       </c>
       <c r="B59" t="n">
-        <v>79631</v>
+        <v>57724</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6875,34 +6870,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451370</v>
+        <v>451153</v>
       </c>
       <c r="R59" t="n">
-        <v>6752389</v>
+        <v>6752545</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7083,39 +7083,35 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129313901</v>
+        <v>129313806</v>
       </c>
       <c r="B61" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -7172,7 +7168,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Bild på gran, garn</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7199,35 +7195,39 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129313806</v>
+        <v>129313901</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Bild på gran, garn</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7420,7 +7420,7 @@
         <v>129309515</v>
       </c>
       <c r="B64" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129309881</v>
+        <v>129316313</v>
       </c>
       <c r="B2" t="n">
         <v>79041</v>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451386</v>
+        <v>451213</v>
       </c>
       <c r="R2" t="n">
-        <v>6752391</v>
+        <v>6752316</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,11 +756,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129316313</v>
+        <v>129309881</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -822,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451213</v>
+        <v>451386</v>
       </c>
       <c r="R3" t="n">
-        <v>6752316</v>
+        <v>6752391</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,6 +863,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129307645</v>
+        <v>129306675</v>
       </c>
       <c r="B5" t="n">
         <v>79041</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451237</v>
+        <v>451206</v>
       </c>
       <c r="R5" t="n">
-        <v>6752478</v>
+        <v>6752540</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129307362</v>
+        <v>129306875</v>
       </c>
       <c r="B6" t="n">
         <v>79041</v>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451244</v>
+        <v>451243</v>
       </c>
       <c r="R6" t="n">
-        <v>6752466</v>
+        <v>6752517</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129306875</v>
+        <v>129307645</v>
       </c>
       <c r="B7" t="n">
         <v>79041</v>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451243</v>
+        <v>451237</v>
       </c>
       <c r="R7" t="n">
-        <v>6752517</v>
+        <v>6752478</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,6 +1301,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129306675</v>
+        <v>129307362</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1362,13 +1367,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451206</v>
+        <v>451244</v>
       </c>
       <c r="R8" t="n">
-        <v>6752540</v>
+        <v>6752466</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1408,11 +1413,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1546,7 +1546,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129307040</v>
+        <v>129307805</v>
       </c>
       <c r="B10" t="n">
         <v>57724</v>
@@ -1577,7 +1577,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451262</v>
+        <v>451335</v>
       </c>
       <c r="R10" t="n">
-        <v>6752514</v>
+        <v>6752504</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129306575</v>
+        <v>129307040</v>
       </c>
       <c r="B11" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,37 +1669,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451153</v>
+        <v>451262</v>
       </c>
       <c r="R11" t="n">
-        <v>6752545</v>
+        <v>6752514</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1872,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129307805</v>
+        <v>129306575</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,39 +1888,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451335</v>
+        <v>451153</v>
       </c>
       <c r="R13" t="n">
-        <v>6752504</v>
+        <v>6752545</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129314017</v>
+        <v>129306457</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451253</v>
+        <v>451149</v>
       </c>
       <c r="R15" t="n">
-        <v>6752304</v>
+        <v>6752603</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,7 +2203,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129306457</v>
+        <v>129306100</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451149</v>
+        <v>451093</v>
       </c>
       <c r="R16" t="n">
-        <v>6752603</v>
+        <v>6752490</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129306100</v>
+        <v>129314017</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451093</v>
+        <v>451253</v>
       </c>
       <c r="R18" t="n">
-        <v>6752490</v>
+        <v>6752304</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2631,32 +2631,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129306556</v>
+        <v>129306511</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451153</v>
+        <v>451170</v>
       </c>
       <c r="R20" t="n">
-        <v>6752545</v>
+        <v>6752562</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2850,32 +2850,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129306511</v>
+        <v>129306556</v>
       </c>
       <c r="B22" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451170</v>
+        <v>451153</v>
       </c>
       <c r="R22" t="n">
-        <v>6752562</v>
+        <v>6752545</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129308422</v>
+        <v>129313973</v>
       </c>
       <c r="B29" t="n">
         <v>79041</v>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>451275</v>
+        <v>451258</v>
       </c>
       <c r="R29" t="n">
-        <v>6752429</v>
+        <v>6752314</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3721,7 +3721,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129306588</v>
+        <v>129308422</v>
       </c>
       <c r="B30" t="n">
         <v>79041</v>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>451153</v>
+        <v>451275</v>
       </c>
       <c r="R30" t="n">
-        <v>6752545</v>
+        <v>6752429</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3935,7 +3935,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129313973</v>
+        <v>129306588</v>
       </c>
       <c r="B32" t="n">
         <v>79041</v>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>451258</v>
+        <v>451153</v>
       </c>
       <c r="R32" t="n">
-        <v>6752314</v>
+        <v>6752545</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4152,7 +4152,7 @@
         <v>129309657</v>
       </c>
       <c r="B34" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4363,10 +4363,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129310178</v>
+        <v>129307777</v>
       </c>
       <c r="B36" t="n">
-        <v>78444</v>
+        <v>79660</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4374,21 +4374,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451435</v>
+        <v>451291</v>
       </c>
       <c r="R36" t="n">
-        <v>6752354</v>
+        <v>6752489</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,10 +4470,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129307777</v>
+        <v>129310178</v>
       </c>
       <c r="B37" t="n">
-        <v>79660</v>
+        <v>78444</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451291</v>
+        <v>451435</v>
       </c>
       <c r="R37" t="n">
-        <v>6752489</v>
+        <v>6752354</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4898,7 +4898,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129307878</v>
+        <v>129313715</v>
       </c>
       <c r="B41" t="n">
         <v>79041</v>
@@ -4933,13 +4933,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451297</v>
+        <v>451335</v>
       </c>
       <c r="R41" t="n">
-        <v>6752466</v>
+        <v>6752312</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4978,12 +4978,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5010,7 +5005,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129313715</v>
+        <v>129307878</v>
       </c>
       <c r="B42" t="n">
         <v>79041</v>
@@ -5045,13 +5040,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451335</v>
+        <v>451297</v>
       </c>
       <c r="R42" t="n">
-        <v>6752312</v>
+        <v>6752466</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5080,7 +5075,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5090,7 +5085,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5229,10 +5229,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129310740</v>
+        <v>129306322</v>
       </c>
       <c r="B44" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5240,21 +5240,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>451416</v>
+        <v>451096</v>
       </c>
       <c r="R44" t="n">
-        <v>6752417</v>
+        <v>6752528</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5336,10 +5336,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129306322</v>
+        <v>129310740</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>451096</v>
+        <v>451416</v>
       </c>
       <c r="R45" t="n">
-        <v>6752528</v>
+        <v>6752417</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129306645</v>
+        <v>129310637</v>
       </c>
       <c r="B46" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451189</v>
+        <v>451442</v>
       </c>
       <c r="R46" t="n">
-        <v>6752531</v>
+        <v>6752403</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,7 +5523,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,10 +5555,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129310637</v>
+        <v>129306645</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5561,21 +5566,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5585,10 +5590,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451442</v>
+        <v>451189</v>
       </c>
       <c r="R47" t="n">
-        <v>6752403</v>
+        <v>6752531</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5620,7 +5625,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5630,12 +5635,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5774,32 +5774,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129310466</v>
+        <v>129307338</v>
       </c>
       <c r="B49" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>451463</v>
+        <v>451244</v>
       </c>
       <c r="R49" t="n">
-        <v>6752384</v>
+        <v>6752466</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5881,32 +5881,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129307338</v>
+        <v>129310466</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451244</v>
+        <v>451463</v>
       </c>
       <c r="R50" t="n">
-        <v>6752466</v>
+        <v>6752384</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129307728</v>
+        <v>129308409</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6111,21 +6111,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6135,13 +6135,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451291</v>
+        <v>451275</v>
       </c>
       <c r="R52" t="n">
-        <v>6752489</v>
+        <v>6752429</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6181,11 +6181,6 @@
       <c r="AB52" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6212,10 +6207,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129308409</v>
+        <v>129307728</v>
       </c>
       <c r="B53" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6223,21 +6218,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6247,13 +6242,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451275</v>
+        <v>451291</v>
       </c>
       <c r="R53" t="n">
-        <v>6752429</v>
+        <v>6752489</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6293,6 +6288,11 @@
       <c r="AB53" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6319,50 +6319,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129306533</v>
+        <v>129307240</v>
       </c>
       <c r="B54" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451170</v>
+        <v>451256</v>
       </c>
       <c r="R54" t="n">
-        <v>6752562</v>
+        <v>6752469</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6431,45 +6426,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129307240</v>
+        <v>129306533</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451256</v>
+        <v>451170</v>
       </c>
       <c r="R55" t="n">
-        <v>6752469</v>
+        <v>6752562</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6538,7 +6538,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129307246</v>
+        <v>129310742</v>
       </c>
       <c r="B56" t="n">
         <v>79041</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451256</v>
+        <v>451416</v>
       </c>
       <c r="R56" t="n">
-        <v>6752469</v>
+        <v>6752417</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6645,7 +6645,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129310742</v>
+        <v>129307246</v>
       </c>
       <c r="B57" t="n">
         <v>79041</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451416</v>
+        <v>451256</v>
       </c>
       <c r="R57" t="n">
-        <v>6752417</v>
+        <v>6752469</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6752,10 +6752,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129309688</v>
+        <v>129306555</v>
       </c>
       <c r="B58" t="n">
-        <v>79631</v>
+        <v>57724</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6763,34 +6763,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451370</v>
+        <v>451153</v>
       </c>
       <c r="R58" t="n">
-        <v>6752389</v>
+        <v>6752545</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6822,7 +6827,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6832,7 +6837,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6859,10 +6864,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129306555</v>
+        <v>129309688</v>
       </c>
       <c r="B59" t="n">
-        <v>57724</v>
+        <v>79631</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6870,39 +6875,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451153</v>
+        <v>451370</v>
       </c>
       <c r="R59" t="n">
-        <v>6752545</v>
+        <v>6752389</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7083,35 +7083,39 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129313806</v>
+        <v>129313901</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -7168,7 +7172,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Bild på gran, garn</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7195,39 +7199,35 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129313901</v>
+        <v>129313806</v>
       </c>
       <c r="B62" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Bild på gran, garn</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129316313</v>
+        <v>129309881</v>
       </c>
       <c r="B2" t="n">
         <v>79041</v>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451213</v>
+        <v>451386</v>
       </c>
       <c r="R2" t="n">
-        <v>6752316</v>
+        <v>6752391</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,6 +756,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129309881</v>
+        <v>129316313</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -817,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451386</v>
+        <v>451213</v>
       </c>
       <c r="R3" t="n">
-        <v>6752391</v>
+        <v>6752316</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,11 +868,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129306675</v>
+        <v>129307645</v>
       </c>
       <c r="B5" t="n">
         <v>79041</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451206</v>
+        <v>451237</v>
       </c>
       <c r="R5" t="n">
-        <v>6752540</v>
+        <v>6752478</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129306875</v>
+        <v>129307362</v>
       </c>
       <c r="B6" t="n">
         <v>79041</v>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451243</v>
+        <v>451244</v>
       </c>
       <c r="R6" t="n">
-        <v>6752517</v>
+        <v>6752466</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129307645</v>
+        <v>129306675</v>
       </c>
       <c r="B7" t="n">
         <v>79041</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451237</v>
+        <v>451206</v>
       </c>
       <c r="R7" t="n">
-        <v>6752478</v>
+        <v>6752540</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1332,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129307362</v>
+        <v>129306875</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451244</v>
+        <v>451243</v>
       </c>
       <c r="R8" t="n">
-        <v>6752466</v>
+        <v>6752517</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129307805</v>
+        <v>129306575</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,39 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451335</v>
+        <v>451153</v>
       </c>
       <c r="R10" t="n">
-        <v>6752504</v>
+        <v>6752545</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129307040</v>
+        <v>129312692</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,42 +1664,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451262</v>
+        <v>451369</v>
       </c>
       <c r="R11" t="n">
-        <v>6752514</v>
+        <v>6752313</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129312692</v>
+        <v>129307805</v>
       </c>
       <c r="B12" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,34 +1771,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451369</v>
+        <v>451335</v>
       </c>
       <c r="R12" t="n">
-        <v>6752313</v>
+        <v>6752504</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1850,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129306575</v>
+        <v>129307040</v>
       </c>
       <c r="B13" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,37 +1883,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451153</v>
+        <v>451262</v>
       </c>
       <c r="R13" t="n">
-        <v>6752545</v>
+        <v>6752514</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129306457</v>
+        <v>129314017</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451149</v>
+        <v>451253</v>
       </c>
       <c r="R15" t="n">
-        <v>6752603</v>
+        <v>6752304</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,7 +2203,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129306100</v>
+        <v>129306457</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451093</v>
+        <v>451149</v>
       </c>
       <c r="R16" t="n">
-        <v>6752490</v>
+        <v>6752603</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129314017</v>
+        <v>129306100</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451253</v>
+        <v>451093</v>
       </c>
       <c r="R18" t="n">
-        <v>6752304</v>
+        <v>6752490</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2738,50 +2738,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129308438</v>
+        <v>129306556</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451260</v>
+        <v>451153</v>
       </c>
       <c r="R21" t="n">
-        <v>6752424</v>
+        <v>6752545</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2850,45 +2845,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129306556</v>
+        <v>129308438</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451153</v>
+        <v>451260</v>
       </c>
       <c r="R22" t="n">
-        <v>6752545</v>
+        <v>6752424</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3614,10 +3614,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129313973</v>
+        <v>129314054</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,21 +3625,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>451258</v>
+        <v>451213</v>
       </c>
       <c r="R29" t="n">
-        <v>6752314</v>
+        <v>6752316</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129306615</v>
+        <v>129306588</v>
       </c>
       <c r="B31" t="n">
         <v>79041</v>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>451164</v>
+        <v>451153</v>
       </c>
       <c r="R31" t="n">
-        <v>6752537</v>
+        <v>6752545</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3935,7 +3935,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129306588</v>
+        <v>129306615</v>
       </c>
       <c r="B32" t="n">
         <v>79041</v>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>451153</v>
+        <v>451164</v>
       </c>
       <c r="R32" t="n">
-        <v>6752545</v>
+        <v>6752537</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4042,10 +4042,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129314054</v>
+        <v>129313973</v>
       </c>
       <c r="B33" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4053,21 +4053,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>451213</v>
+        <v>451258</v>
       </c>
       <c r="R33" t="n">
-        <v>6752316</v>
+        <v>6752314</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4149,32 +4149,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129309657</v>
+        <v>129310404</v>
       </c>
       <c r="B34" t="n">
-        <v>92822</v>
+        <v>79631</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451370</v>
+        <v>451456</v>
       </c>
       <c r="R34" t="n">
-        <v>6752389</v>
+        <v>6752426</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129311235</v>
+        <v>129307777</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451357</v>
+        <v>451291</v>
       </c>
       <c r="R35" t="n">
-        <v>6752476</v>
+        <v>6752489</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4363,10 +4363,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129307777</v>
+        <v>129311235</v>
       </c>
       <c r="B36" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4374,21 +4374,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451291</v>
+        <v>451357</v>
       </c>
       <c r="R36" t="n">
-        <v>6752489</v>
+        <v>6752476</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4577,32 +4577,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129310404</v>
+        <v>129309657</v>
       </c>
       <c r="B38" t="n">
-        <v>79631</v>
+        <v>92822</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451456</v>
+        <v>451370</v>
       </c>
       <c r="R38" t="n">
-        <v>6752426</v>
+        <v>6752389</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4898,7 +4898,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129313715</v>
+        <v>129307878</v>
       </c>
       <c r="B41" t="n">
         <v>79041</v>
@@ -4933,13 +4933,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451335</v>
+        <v>451297</v>
       </c>
       <c r="R41" t="n">
-        <v>6752312</v>
+        <v>6752466</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4978,7 +4978,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5005,7 +5010,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129307878</v>
+        <v>129313715</v>
       </c>
       <c r="B42" t="n">
         <v>79041</v>
@@ -5040,13 +5045,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451297</v>
+        <v>451335</v>
       </c>
       <c r="R42" t="n">
-        <v>6752466</v>
+        <v>6752312</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5075,7 +5080,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5085,12 +5090,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129310637</v>
+        <v>129306645</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451442</v>
+        <v>451189</v>
       </c>
       <c r="R46" t="n">
-        <v>6752403</v>
+        <v>6752531</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,12 +5523,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5555,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129306645</v>
+        <v>129310637</v>
       </c>
       <c r="B47" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5566,21 +5561,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5590,10 +5585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451189</v>
+        <v>451442</v>
       </c>
       <c r="R47" t="n">
-        <v>6752531</v>
+        <v>6752403</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5625,7 +5620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5635,7 +5630,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5988,10 +5988,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129308051</v>
+        <v>129308409</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5999,21 +5999,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6023,13 +6023,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451352</v>
+        <v>451275</v>
       </c>
       <c r="R51" t="n">
-        <v>6752454</v>
+        <v>6752429</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6069,11 +6069,6 @@
       <c r="AB51" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6100,32 +6095,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129308409</v>
+        <v>129307240</v>
       </c>
       <c r="B52" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6135,10 +6130,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451275</v>
+        <v>451256</v>
       </c>
       <c r="R52" t="n">
-        <v>6752429</v>
+        <v>6752469</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6207,7 +6202,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129307728</v>
+        <v>129308051</v>
       </c>
       <c r="B53" t="n">
         <v>79041</v>
@@ -6242,10 +6237,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451291</v>
+        <v>451352</v>
       </c>
       <c r="R53" t="n">
-        <v>6752489</v>
+        <v>6752454</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6319,32 +6314,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129307240</v>
+        <v>129307728</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6354,13 +6349,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451256</v>
+        <v>451291</v>
       </c>
       <c r="R54" t="n">
-        <v>6752469</v>
+        <v>6752489</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6400,6 +6395,11 @@
       <c r="AB54" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6538,10 +6538,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129310742</v>
+        <v>129306555</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6549,34 +6549,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451416</v>
+        <v>451153</v>
       </c>
       <c r="R56" t="n">
-        <v>6752417</v>
+        <v>6752545</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6608,7 +6613,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6618,7 +6623,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6645,10 +6650,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129307246</v>
+        <v>129309688</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6656,21 +6661,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6680,10 +6685,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451256</v>
+        <v>451370</v>
       </c>
       <c r="R57" t="n">
-        <v>6752469</v>
+        <v>6752389</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6715,7 +6720,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6725,7 +6730,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6752,10 +6757,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129306555</v>
+        <v>129307246</v>
       </c>
       <c r="B58" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6763,39 +6768,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451153</v>
+        <v>451256</v>
       </c>
       <c r="R58" t="n">
-        <v>6752545</v>
+        <v>6752469</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6864,10 +6864,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129309688</v>
+        <v>129310742</v>
       </c>
       <c r="B59" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6875,21 +6875,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451370</v>
+        <v>451416</v>
       </c>
       <c r="R59" t="n">
-        <v>6752389</v>
+        <v>6752417</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7083,39 +7083,35 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129313901</v>
+        <v>129313806</v>
       </c>
       <c r="B61" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -7172,7 +7168,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Bild på gran, garn</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7199,35 +7195,39 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129313806</v>
+        <v>129313901</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Bild på gran, garn</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129309881</v>
+        <v>129316313</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451386</v>
+        <v>451213</v>
       </c>
       <c r="R2" t="n">
-        <v>6752391</v>
+        <v>6752316</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,11 +756,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129316313</v>
+        <v>129309881</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451213</v>
+        <v>451386</v>
       </c>
       <c r="R3" t="n">
-        <v>6752316</v>
+        <v>6752391</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,6 +863,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129307645</v>
+        <v>129306675</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451237</v>
+        <v>451206</v>
       </c>
       <c r="R5" t="n">
-        <v>6752478</v>
+        <v>6752540</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129307362</v>
+        <v>129306875</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451244</v>
+        <v>451243</v>
       </c>
       <c r="R6" t="n">
-        <v>6752466</v>
+        <v>6752517</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129306675</v>
+        <v>129307645</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451206</v>
+        <v>451237</v>
       </c>
       <c r="R7" t="n">
-        <v>6752540</v>
+        <v>6752478</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129306875</v>
+        <v>129307362</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451243</v>
+        <v>451244</v>
       </c>
       <c r="R8" t="n">
-        <v>6752517</v>
+        <v>6752466</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129306575</v>
+        <v>129312692</v>
       </c>
       <c r="B10" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451153</v>
+        <v>451369</v>
       </c>
       <c r="R10" t="n">
-        <v>6752545</v>
+        <v>6752313</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129312692</v>
+        <v>129306575</v>
       </c>
       <c r="B11" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451369</v>
+        <v>451153</v>
       </c>
       <c r="R11" t="n">
-        <v>6752313</v>
+        <v>6752545</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2096,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129314017</v>
+        <v>129306457</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451253</v>
+        <v>451149</v>
       </c>
       <c r="R15" t="n">
-        <v>6752304</v>
+        <v>6752603</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129306457</v>
+        <v>129306100</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451149</v>
+        <v>451093</v>
       </c>
       <c r="R16" t="n">
-        <v>6752603</v>
+        <v>6752490</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2313,7 +2313,7 @@
         <v>129306554</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129306100</v>
+        <v>129314017</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451093</v>
+        <v>451253</v>
       </c>
       <c r="R18" t="n">
-        <v>6752490</v>
+        <v>6752304</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2634,7 +2634,7 @@
         <v>129306511</v>
       </c>
       <c r="B20" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,45 +2738,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129306556</v>
+        <v>129308438</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451153</v>
+        <v>451260</v>
       </c>
       <c r="R21" t="n">
-        <v>6752545</v>
+        <v>6752424</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2845,50 +2850,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129308438</v>
+        <v>129306556</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451260</v>
+        <v>451153</v>
       </c>
       <c r="R22" t="n">
-        <v>6752424</v>
+        <v>6752545</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2957,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129311305</v>
+        <v>129307237</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,37 +2968,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451358</v>
+        <v>451256</v>
       </c>
       <c r="R23" t="n">
-        <v>6752424</v>
+        <v>6752469</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3027,7 +3032,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3037,12 +3042,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,10 +3069,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129307012</v>
+        <v>129311305</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3104,10 +3104,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451262</v>
+        <v>451358</v>
       </c>
       <c r="R24" t="n">
-        <v>6752514</v>
+        <v>6752424</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3181,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129307237</v>
+        <v>129307012</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,42 +3192,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451256</v>
+        <v>451262</v>
       </c>
       <c r="R25" t="n">
-        <v>6752469</v>
+        <v>6752514</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3267,6 +3262,11 @@
       <c r="AB25" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,7 +3296,7 @@
         <v>129308406</v>
       </c>
       <c r="B26" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>129306315</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>129314054</v>
       </c>
       <c r="B29" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3721,10 +3721,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129308422</v>
+        <v>129313973</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>451275</v>
+        <v>451258</v>
       </c>
       <c r="R30" t="n">
-        <v>6752429</v>
+        <v>6752314</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3828,10 +3828,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129306588</v>
+        <v>129308422</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>451153</v>
+        <v>451275</v>
       </c>
       <c r="R31" t="n">
-        <v>6752545</v>
+        <v>6752429</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3938,7 +3938,7 @@
         <v>129306615</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4042,10 +4042,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129313973</v>
+        <v>129306588</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>451258</v>
+        <v>451153</v>
       </c>
       <c r="R33" t="n">
-        <v>6752314</v>
+        <v>6752545</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4149,32 +4149,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129310404</v>
+        <v>129309657</v>
       </c>
       <c r="B34" t="n">
-        <v>79631</v>
+        <v>92825</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451456</v>
+        <v>451370</v>
       </c>
       <c r="R34" t="n">
-        <v>6752426</v>
+        <v>6752389</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129307777</v>
+        <v>129311235</v>
       </c>
       <c r="B35" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451291</v>
+        <v>451357</v>
       </c>
       <c r="R35" t="n">
-        <v>6752489</v>
+        <v>6752476</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4363,10 +4363,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129311235</v>
+        <v>129307777</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4374,21 +4374,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451357</v>
+        <v>451291</v>
       </c>
       <c r="R36" t="n">
-        <v>6752476</v>
+        <v>6752489</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4473,7 +4473,7 @@
         <v>129310178</v>
       </c>
       <c r="B37" t="n">
-        <v>78444</v>
+        <v>78446</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4577,32 +4577,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129309657</v>
+        <v>129310404</v>
       </c>
       <c r="B38" t="n">
-        <v>92822</v>
+        <v>79633</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451370</v>
+        <v>451456</v>
       </c>
       <c r="R38" t="n">
-        <v>6752389</v>
+        <v>6752426</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4687,7 +4687,7 @@
         <v>129307775</v>
       </c>
       <c r="B39" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>129306610</v>
       </c>
       <c r="B40" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129307878</v>
+        <v>129313715</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4933,13 +4933,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451297</v>
+        <v>451335</v>
       </c>
       <c r="R41" t="n">
-        <v>6752466</v>
+        <v>6752312</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4978,12 +4978,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5010,10 +5005,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129313715</v>
+        <v>129307878</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5045,13 +5040,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451335</v>
+        <v>451297</v>
       </c>
       <c r="R42" t="n">
-        <v>6752312</v>
+        <v>6752466</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5080,7 +5075,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5090,7 +5085,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5120,7 +5120,7 @@
         <v>129310209</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>129306322</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>129310740</v>
       </c>
       <c r="B45" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129306645</v>
+        <v>129310637</v>
       </c>
       <c r="B46" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451189</v>
+        <v>451442</v>
       </c>
       <c r="R46" t="n">
-        <v>6752531</v>
+        <v>6752403</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,7 +5523,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,10 +5555,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129310637</v>
+        <v>129306645</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5561,21 +5566,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5585,10 +5590,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451442</v>
+        <v>451189</v>
       </c>
       <c r="R47" t="n">
-        <v>6752403</v>
+        <v>6752531</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5620,7 +5625,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5630,12 +5635,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5662,10 +5662,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129307334</v>
+        <v>129310466</v>
       </c>
       <c r="B48" t="n">
-        <v>57724</v>
+        <v>79662</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5673,39 +5673,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451244</v>
+        <v>451463</v>
       </c>
       <c r="R48" t="n">
-        <v>6752466</v>
+        <v>6752384</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5737,7 +5732,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5747,7 +5742,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5774,35 +5769,40 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129307338</v>
+        <v>129307334</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -5881,32 +5881,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129310466</v>
+        <v>129307338</v>
       </c>
       <c r="B50" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451463</v>
+        <v>451244</v>
       </c>
       <c r="R50" t="n">
-        <v>6752384</v>
+        <v>6752466</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5988,10 +5988,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129308409</v>
+        <v>129308051</v>
       </c>
       <c r="B51" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5999,21 +5999,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6023,13 +6023,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451275</v>
+        <v>451352</v>
       </c>
       <c r="R51" t="n">
-        <v>6752429</v>
+        <v>6752454</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6069,6 +6069,11 @@
       <c r="AB51" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6095,32 +6100,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129307240</v>
+        <v>129308409</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>79662</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6130,10 +6135,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451256</v>
+        <v>451275</v>
       </c>
       <c r="R52" t="n">
-        <v>6752469</v>
+        <v>6752429</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6202,10 +6207,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129308051</v>
+        <v>129307728</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6237,10 +6242,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451352</v>
+        <v>451291</v>
       </c>
       <c r="R53" t="n">
-        <v>6752454</v>
+        <v>6752489</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6314,10 +6319,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129307728</v>
+        <v>129306533</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6325,37 +6330,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451291</v>
+        <v>451170</v>
       </c>
       <c r="R54" t="n">
-        <v>6752489</v>
+        <v>6752562</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6395,11 +6405,6 @@
       <c r="AB54" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6426,50 +6431,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129306533</v>
+        <v>129307240</v>
       </c>
       <c r="B55" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451170</v>
+        <v>451256</v>
       </c>
       <c r="R55" t="n">
-        <v>6752562</v>
+        <v>6752469</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6650,10 +6650,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129309688</v>
+        <v>129310742</v>
       </c>
       <c r="B57" t="n">
-        <v>79631</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6661,21 +6661,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6685,10 +6685,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451370</v>
+        <v>451416</v>
       </c>
       <c r="R57" t="n">
-        <v>6752389</v>
+        <v>6752417</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6760,7 +6760,7 @@
         <v>129307246</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129310742</v>
+        <v>129309688</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>79633</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6875,21 +6875,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451416</v>
+        <v>451370</v>
       </c>
       <c r="R59" t="n">
-        <v>6752417</v>
+        <v>6752389</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6974,7 +6974,7 @@
         <v>129310867</v>
       </c>
       <c r="B60" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>129313806</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>129313901</v>
       </c>
       <c r="B62" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>129322141</v>
       </c>
       <c r="B63" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>129309515</v>
       </c>
       <c r="B64" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -1760,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129307805</v>
+        <v>129307040</v>
       </c>
       <c r="B12" t="n">
         <v>57724</v>
@@ -1791,7 +1791,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1800,13 +1800,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451335</v>
+        <v>451262</v>
       </c>
       <c r="R12" t="n">
-        <v>6752504</v>
+        <v>6752514</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129307040</v>
+        <v>129307805</v>
       </c>
       <c r="B13" t="n">
         <v>57724</v>
@@ -1903,7 +1903,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451262</v>
+        <v>451335</v>
       </c>
       <c r="R13" t="n">
-        <v>6752514</v>
+        <v>6752504</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2957,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129307237</v>
+        <v>129311305</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,42 +2968,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451256</v>
+        <v>451358</v>
       </c>
       <c r="R23" t="n">
-        <v>6752469</v>
+        <v>6752424</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3032,7 +3027,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3042,7 +3037,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,7 +3069,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129311305</v>
+        <v>129307012</v>
       </c>
       <c r="B24" t="n">
         <v>79043</v>
@@ -3104,10 +3104,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451358</v>
+        <v>451262</v>
       </c>
       <c r="R24" t="n">
-        <v>6752424</v>
+        <v>6752514</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3181,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129307012</v>
+        <v>129307237</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,37 +3192,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451262</v>
+        <v>451256</v>
       </c>
       <c r="R25" t="n">
-        <v>6752514</v>
+        <v>6752469</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3262,11 +3267,6 @@
       <c r="AB25" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4149,32 +4149,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129309657</v>
+        <v>129310404</v>
       </c>
       <c r="B34" t="n">
-        <v>92825</v>
+        <v>79633</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451370</v>
+        <v>451456</v>
       </c>
       <c r="R34" t="n">
-        <v>6752389</v>
+        <v>6752426</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4256,32 +4256,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129311235</v>
+        <v>129309657</v>
       </c>
       <c r="B35" t="n">
-        <v>79043</v>
+        <v>92825</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451357</v>
+        <v>451370</v>
       </c>
       <c r="R35" t="n">
-        <v>6752476</v>
+        <v>6752389</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4363,10 +4363,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129307777</v>
+        <v>129311235</v>
       </c>
       <c r="B36" t="n">
-        <v>79662</v>
+        <v>79043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4374,21 +4374,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451291</v>
+        <v>451357</v>
       </c>
       <c r="R36" t="n">
-        <v>6752489</v>
+        <v>6752476</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,10 +4470,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129310178</v>
+        <v>129307777</v>
       </c>
       <c r="B37" t="n">
-        <v>78446</v>
+        <v>79662</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451435</v>
+        <v>451291</v>
       </c>
       <c r="R37" t="n">
-        <v>6752354</v>
+        <v>6752489</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4577,10 +4577,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129310404</v>
+        <v>129310178</v>
       </c>
       <c r="B38" t="n">
-        <v>79633</v>
+        <v>78446</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451456</v>
+        <v>451435</v>
       </c>
       <c r="R38" t="n">
-        <v>6752426</v>
+        <v>6752354</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129316313</v>
+        <v>129309881</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451213</v>
+        <v>451386</v>
       </c>
       <c r="R2" t="n">
-        <v>6752316</v>
+        <v>6752391</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,6 +756,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129309881</v>
+        <v>129316313</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451386</v>
+        <v>451213</v>
       </c>
       <c r="R3" t="n">
-        <v>6752391</v>
+        <v>6752316</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,11 +868,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129306675</v>
+        <v>129307645</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451206</v>
+        <v>451237</v>
       </c>
       <c r="R5" t="n">
-        <v>6752540</v>
+        <v>6752478</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129306875</v>
+        <v>129307362</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451243</v>
+        <v>451244</v>
       </c>
       <c r="R6" t="n">
-        <v>6752517</v>
+        <v>6752466</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129307645</v>
+        <v>129306875</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451237</v>
+        <v>451243</v>
       </c>
       <c r="R7" t="n">
-        <v>6752478</v>
+        <v>6752517</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,11 +1301,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129307362</v>
+        <v>129306675</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451244</v>
+        <v>451206</v>
       </c>
       <c r="R8" t="n">
-        <v>6752466</v>
+        <v>6752540</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,6 +1408,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129312692</v>
+        <v>129306575</v>
       </c>
       <c r="B10" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451369</v>
+        <v>451153</v>
       </c>
       <c r="R10" t="n">
-        <v>6752313</v>
+        <v>6752545</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129306575</v>
+        <v>129312692</v>
       </c>
       <c r="B11" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451153</v>
+        <v>451369</v>
       </c>
       <c r="R11" t="n">
-        <v>6752545</v>
+        <v>6752313</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129307040</v>
+        <v>129307805</v>
       </c>
       <c r="B12" t="n">
         <v>57724</v>
@@ -1791,7 +1791,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1800,13 +1800,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451262</v>
+        <v>451335</v>
       </c>
       <c r="R12" t="n">
-        <v>6752514</v>
+        <v>6752504</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129307805</v>
+        <v>129307040</v>
       </c>
       <c r="B13" t="n">
         <v>57724</v>
@@ -1903,7 +1903,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451335</v>
+        <v>451262</v>
       </c>
       <c r="R13" t="n">
-        <v>6752504</v>
+        <v>6752514</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129306457</v>
+        <v>129314017</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451149</v>
+        <v>451253</v>
       </c>
       <c r="R15" t="n">
-        <v>6752603</v>
+        <v>6752304</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129306100</v>
+        <v>129306457</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451093</v>
+        <v>451149</v>
       </c>
       <c r="R16" t="n">
-        <v>6752490</v>
+        <v>6752603</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2313,7 +2313,7 @@
         <v>129306554</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129314017</v>
+        <v>129306100</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451253</v>
+        <v>451093</v>
       </c>
       <c r="R18" t="n">
-        <v>6752304</v>
+        <v>6752490</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2634,7 +2634,7 @@
         <v>129306511</v>
       </c>
       <c r="B20" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2957,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129311305</v>
+        <v>129307237</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,37 +2968,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451358</v>
+        <v>451256</v>
       </c>
       <c r="R23" t="n">
-        <v>6752424</v>
+        <v>6752469</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3027,7 +3032,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3037,12 +3042,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,10 +3069,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129307012</v>
+        <v>129311305</v>
       </c>
       <c r="B24" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3104,10 +3104,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451262</v>
+        <v>451358</v>
       </c>
       <c r="R24" t="n">
-        <v>6752514</v>
+        <v>6752424</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3181,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129307237</v>
+        <v>129307012</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,42 +3192,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451256</v>
+        <v>451262</v>
       </c>
       <c r="R25" t="n">
-        <v>6752469</v>
+        <v>6752514</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3267,6 +3262,11 @@
       <c r="AB25" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,7 +3296,7 @@
         <v>129308406</v>
       </c>
       <c r="B26" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>129306315</v>
       </c>
       <c r="B27" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129314054</v>
+        <v>129308422</v>
       </c>
       <c r="B29" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,21 +3625,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>451213</v>
+        <v>451275</v>
       </c>
       <c r="R29" t="n">
-        <v>6752316</v>
+        <v>6752429</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3721,10 +3721,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129313973</v>
+        <v>129306588</v>
       </c>
       <c r="B30" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>451258</v>
+        <v>451153</v>
       </c>
       <c r="R30" t="n">
-        <v>6752314</v>
+        <v>6752545</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3828,10 +3828,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129308422</v>
+        <v>129306615</v>
       </c>
       <c r="B31" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>451275</v>
+        <v>451164</v>
       </c>
       <c r="R31" t="n">
-        <v>6752429</v>
+        <v>6752537</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129306615</v>
+        <v>129313973</v>
       </c>
       <c r="B32" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>451164</v>
+        <v>451258</v>
       </c>
       <c r="R32" t="n">
-        <v>6752537</v>
+        <v>6752314</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4042,10 +4042,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129306588</v>
+        <v>129314054</v>
       </c>
       <c r="B33" t="n">
-        <v>79043</v>
+        <v>78802</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4053,21 +4053,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>451153</v>
+        <v>451213</v>
       </c>
       <c r="R33" t="n">
-        <v>6752545</v>
+        <v>6752316</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4149,32 +4149,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129310404</v>
+        <v>129309657</v>
       </c>
       <c r="B34" t="n">
-        <v>79633</v>
+        <v>92827</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451456</v>
+        <v>451370</v>
       </c>
       <c r="R34" t="n">
-        <v>6752426</v>
+        <v>6752389</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4256,32 +4256,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129309657</v>
+        <v>129310404</v>
       </c>
       <c r="B35" t="n">
-        <v>92825</v>
+        <v>79634</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451370</v>
+        <v>451456</v>
       </c>
       <c r="R35" t="n">
-        <v>6752389</v>
+        <v>6752426</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4363,10 +4363,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129311235</v>
+        <v>129307777</v>
       </c>
       <c r="B36" t="n">
-        <v>79043</v>
+        <v>79663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4374,21 +4374,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451357</v>
+        <v>451291</v>
       </c>
       <c r="R36" t="n">
-        <v>6752476</v>
+        <v>6752489</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,10 +4470,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129307777</v>
+        <v>129311235</v>
       </c>
       <c r="B37" t="n">
-        <v>79662</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451291</v>
+        <v>451357</v>
       </c>
       <c r="R37" t="n">
-        <v>6752489</v>
+        <v>6752476</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4580,7 +4580,7 @@
         <v>129310178</v>
       </c>
       <c r="B38" t="n">
-        <v>78446</v>
+        <v>78447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>129307775</v>
       </c>
       <c r="B39" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>129306610</v>
       </c>
       <c r="B40" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129313715</v>
+        <v>129307878</v>
       </c>
       <c r="B41" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4933,13 +4933,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451335</v>
+        <v>451297</v>
       </c>
       <c r="R41" t="n">
-        <v>6752312</v>
+        <v>6752466</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4978,7 +4978,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5005,10 +5010,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129307878</v>
+        <v>129313715</v>
       </c>
       <c r="B42" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5040,13 +5045,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451297</v>
+        <v>451335</v>
       </c>
       <c r="R42" t="n">
-        <v>6752466</v>
+        <v>6752312</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5075,7 +5080,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5085,12 +5090,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5120,7 +5120,7 @@
         <v>129310209</v>
       </c>
       <c r="B43" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5229,10 +5229,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129306322</v>
+        <v>129310740</v>
       </c>
       <c r="B44" t="n">
-        <v>79043</v>
+        <v>79663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5240,21 +5240,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>451096</v>
+        <v>451416</v>
       </c>
       <c r="R44" t="n">
-        <v>6752528</v>
+        <v>6752417</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5336,10 +5336,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129310740</v>
+        <v>129306322</v>
       </c>
       <c r="B45" t="n">
-        <v>79662</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>451416</v>
+        <v>451096</v>
       </c>
       <c r="R45" t="n">
-        <v>6752417</v>
+        <v>6752528</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129310637</v>
+        <v>129306645</v>
       </c>
       <c r="B46" t="n">
-        <v>79043</v>
+        <v>79663</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451442</v>
+        <v>451189</v>
       </c>
       <c r="R46" t="n">
-        <v>6752403</v>
+        <v>6752531</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,12 +5523,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5555,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129306645</v>
+        <v>129310637</v>
       </c>
       <c r="B47" t="n">
-        <v>79662</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5566,21 +5561,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5590,10 +5585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451189</v>
+        <v>451442</v>
       </c>
       <c r="R47" t="n">
-        <v>6752531</v>
+        <v>6752403</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5625,7 +5620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5635,7 +5630,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5665,7 +5665,7 @@
         <v>129310466</v>
       </c>
       <c r="B48" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5988,32 +5988,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129308051</v>
+        <v>129307240</v>
       </c>
       <c r="B51" t="n">
-        <v>79043</v>
+        <v>8450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6023,13 +6023,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451352</v>
+        <v>451256</v>
       </c>
       <c r="R51" t="n">
-        <v>6752454</v>
+        <v>6752469</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6069,11 +6069,6 @@
       <c r="AB51" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6100,10 +6095,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129308409</v>
+        <v>129308051</v>
       </c>
       <c r="B52" t="n">
-        <v>79662</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6111,21 +6106,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6135,13 +6130,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451275</v>
+        <v>451352</v>
       </c>
       <c r="R52" t="n">
-        <v>6752429</v>
+        <v>6752454</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6181,6 +6176,11 @@
       <c r="AB52" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6210,7 +6210,7 @@
         <v>129307728</v>
       </c>
       <c r="B53" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6431,32 +6431,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129307240</v>
+        <v>129308409</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6466,10 +6466,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451256</v>
+        <v>451275</v>
       </c>
       <c r="R55" t="n">
-        <v>6752469</v>
+        <v>6752429</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6538,10 +6538,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129306555</v>
+        <v>129307246</v>
       </c>
       <c r="B56" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6549,39 +6549,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451153</v>
+        <v>451256</v>
       </c>
       <c r="R56" t="n">
-        <v>6752545</v>
+        <v>6752469</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6653,7 +6648,7 @@
         <v>129310742</v>
       </c>
       <c r="B57" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6757,10 +6752,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129307246</v>
+        <v>129306555</v>
       </c>
       <c r="B58" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6768,34 +6763,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451256</v>
+        <v>451153</v>
       </c>
       <c r="R58" t="n">
-        <v>6752469</v>
+        <v>6752545</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6867,7 +6867,7 @@
         <v>129309688</v>
       </c>
       <c r="B59" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>129310867</v>
       </c>
       <c r="B60" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>129313806</v>
       </c>
       <c r="B61" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>129313901</v>
       </c>
       <c r="B62" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>129322141</v>
       </c>
       <c r="B63" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>129309515</v>
       </c>
       <c r="B64" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -1760,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129307805</v>
+        <v>129307040</v>
       </c>
       <c r="B12" t="n">
         <v>57724</v>
@@ -1791,7 +1791,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1800,13 +1800,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451335</v>
+        <v>451262</v>
       </c>
       <c r="R12" t="n">
-        <v>6752504</v>
+        <v>6752514</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129307040</v>
+        <v>129307805</v>
       </c>
       <c r="B13" t="n">
         <v>57724</v>
@@ -1903,7 +1903,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451262</v>
+        <v>451335</v>
       </c>
       <c r="R13" t="n">
-        <v>6752514</v>
+        <v>6752504</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2096,32 +2096,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129314017</v>
+        <v>129307042</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,13 +2131,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451253</v>
+        <v>451262</v>
       </c>
       <c r="R15" t="n">
-        <v>6752304</v>
+        <v>6752514</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,7 +2203,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129306457</v>
+        <v>129314017</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451149</v>
+        <v>451253</v>
       </c>
       <c r="R16" t="n">
-        <v>6752603</v>
+        <v>6752304</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,7 +2310,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129306554</v>
+        <v>129306457</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451170</v>
+        <v>451149</v>
       </c>
       <c r="R17" t="n">
-        <v>6752562</v>
+        <v>6752603</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129306100</v>
+        <v>129306554</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451093</v>
+        <v>451170</v>
       </c>
       <c r="R18" t="n">
-        <v>6752490</v>
+        <v>6752562</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2524,32 +2524,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129307042</v>
+        <v>129306100</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,13 +2559,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451262</v>
+        <v>451093</v>
       </c>
       <c r="R19" t="n">
-        <v>6752514</v>
+        <v>6752490</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2957,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129307237</v>
+        <v>129311305</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,42 +2968,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451256</v>
+        <v>451358</v>
       </c>
       <c r="R23" t="n">
-        <v>6752469</v>
+        <v>6752424</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3032,7 +3027,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3042,7 +3037,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,7 +3069,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129311305</v>
+        <v>129307012</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3104,10 +3104,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451358</v>
+        <v>451262</v>
       </c>
       <c r="R24" t="n">
-        <v>6752424</v>
+        <v>6752514</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3181,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129307012</v>
+        <v>129308406</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,21 +3192,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3216,13 +3216,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451262</v>
+        <v>451275</v>
       </c>
       <c r="R25" t="n">
-        <v>6752514</v>
+        <v>6752429</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3262,11 +3262,6 @@
       <c r="AB25" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3293,10 +3288,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129308406</v>
+        <v>129307237</v>
       </c>
       <c r="B26" t="n">
-        <v>79634</v>
+        <v>57724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3304,34 +3299,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451275</v>
+        <v>451256</v>
       </c>
       <c r="R26" t="n">
-        <v>6752429</v>
+        <v>6752469</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4149,32 +4149,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129309657</v>
+        <v>129310404</v>
       </c>
       <c r="B34" t="n">
-        <v>92827</v>
+        <v>79634</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451370</v>
+        <v>451456</v>
       </c>
       <c r="R34" t="n">
-        <v>6752389</v>
+        <v>6752426</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129310404</v>
+        <v>129311235</v>
       </c>
       <c r="B35" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451456</v>
+        <v>451357</v>
       </c>
       <c r="R35" t="n">
-        <v>6752426</v>
+        <v>6752476</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4363,32 +4363,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129307777</v>
+        <v>129309657</v>
       </c>
       <c r="B36" t="n">
-        <v>79663</v>
+        <v>92831</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451291</v>
+        <v>451370</v>
       </c>
       <c r="R36" t="n">
-        <v>6752489</v>
+        <v>6752389</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,10 +4470,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129311235</v>
+        <v>129310178</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>78447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451357</v>
+        <v>451435</v>
       </c>
       <c r="R37" t="n">
-        <v>6752476</v>
+        <v>6752354</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4577,10 +4577,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129310178</v>
+        <v>129307777</v>
       </c>
       <c r="B38" t="n">
-        <v>78447</v>
+        <v>79663</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4612,13 +4612,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451435</v>
+        <v>451291</v>
       </c>
       <c r="R38" t="n">
-        <v>6752354</v>
+        <v>6752489</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129306645</v>
+        <v>129310637</v>
       </c>
       <c r="B46" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451189</v>
+        <v>451442</v>
       </c>
       <c r="R46" t="n">
-        <v>6752531</v>
+        <v>6752403</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,7 +5523,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,10 +5555,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129310637</v>
+        <v>129306645</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5561,21 +5566,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5585,10 +5590,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451442</v>
+        <v>451189</v>
       </c>
       <c r="R47" t="n">
-        <v>6752403</v>
+        <v>6752531</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5620,7 +5625,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5630,12 +5635,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5662,10 +5662,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129310466</v>
+        <v>129307334</v>
       </c>
       <c r="B48" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5673,34 +5673,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451463</v>
+        <v>451244</v>
       </c>
       <c r="R48" t="n">
-        <v>6752384</v>
+        <v>6752466</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5732,7 +5737,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5742,7 +5747,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5769,40 +5774,35 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129307334</v>
+        <v>129307338</v>
       </c>
       <c r="B49" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -5881,32 +5881,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129307338</v>
+        <v>129310466</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451244</v>
+        <v>451463</v>
       </c>
       <c r="R50" t="n">
-        <v>6752466</v>
+        <v>6752384</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6095,10 +6095,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129308051</v>
+        <v>129308409</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6106,21 +6106,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6130,13 +6130,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451352</v>
+        <v>451275</v>
       </c>
       <c r="R52" t="n">
-        <v>6752454</v>
+        <v>6752429</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6176,11 +6176,6 @@
       <c r="AB52" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6207,7 +6202,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129307728</v>
+        <v>129308051</v>
       </c>
       <c r="B53" t="n">
         <v>79044</v>
@@ -6242,10 +6237,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451291</v>
+        <v>451352</v>
       </c>
       <c r="R53" t="n">
-        <v>6752489</v>
+        <v>6752454</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6319,10 +6314,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129306533</v>
+        <v>129307728</v>
       </c>
       <c r="B54" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6330,42 +6325,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451170</v>
+        <v>451291</v>
       </c>
       <c r="R54" t="n">
-        <v>6752562</v>
+        <v>6752489</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6405,6 +6395,11 @@
       <c r="AB54" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6431,10 +6426,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129308409</v>
+        <v>129306533</v>
       </c>
       <c r="B55" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6442,34 +6437,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451275</v>
+        <v>451170</v>
       </c>
       <c r="R55" t="n">
-        <v>6752429</v>
+        <v>6752562</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7198,7 +7198,7 @@
         <v>129313901</v>
       </c>
       <c r="B62" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>129309515</v>
       </c>
       <c r="B64" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129309881</v>
+        <v>129306536</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451386</v>
+        <v>451170</v>
       </c>
       <c r="R2" t="n">
-        <v>6752391</v>
+        <v>6752562</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129316313</v>
+        <v>129309881</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -822,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451213</v>
+        <v>451386</v>
       </c>
       <c r="R3" t="n">
-        <v>6752316</v>
+        <v>6752391</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,6 +863,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129306536</v>
+        <v>129316313</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451170</v>
+        <v>451213</v>
       </c>
       <c r="R4" t="n">
-        <v>6752562</v>
+        <v>6752316</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1760,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129307040</v>
+        <v>129307805</v>
       </c>
       <c r="B12" t="n">
         <v>57724</v>
@@ -1791,7 +1791,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1800,13 +1800,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451262</v>
+        <v>451335</v>
       </c>
       <c r="R12" t="n">
-        <v>6752514</v>
+        <v>6752504</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129307805</v>
+        <v>129307040</v>
       </c>
       <c r="B13" t="n">
         <v>57724</v>
@@ -1903,7 +1903,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451335</v>
+        <v>451262</v>
       </c>
       <c r="R13" t="n">
-        <v>6752504</v>
+        <v>6752514</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2096,32 +2096,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129307042</v>
+        <v>129314017</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,13 +2131,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451262</v>
+        <v>451253</v>
       </c>
       <c r="R15" t="n">
-        <v>6752514</v>
+        <v>6752304</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,7 +2203,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129314017</v>
+        <v>129306457</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451253</v>
+        <v>451149</v>
       </c>
       <c r="R16" t="n">
-        <v>6752304</v>
+        <v>6752603</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,7 +2310,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129306457</v>
+        <v>129306554</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451149</v>
+        <v>451170</v>
       </c>
       <c r="R17" t="n">
-        <v>6752603</v>
+        <v>6752562</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129306554</v>
+        <v>129306100</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451170</v>
+        <v>451093</v>
       </c>
       <c r="R18" t="n">
-        <v>6752562</v>
+        <v>6752490</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2524,32 +2524,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129306100</v>
+        <v>129307042</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,13 +2559,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451093</v>
+        <v>451262</v>
       </c>
       <c r="R19" t="n">
-        <v>6752490</v>
+        <v>6752514</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3181,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129308406</v>
+        <v>129307237</v>
       </c>
       <c r="B25" t="n">
-        <v>79634</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,34 +3192,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451275</v>
+        <v>451256</v>
       </c>
       <c r="R25" t="n">
-        <v>6752429</v>
+        <v>6752469</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3288,10 +3293,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129307237</v>
+        <v>129308406</v>
       </c>
       <c r="B26" t="n">
-        <v>57724</v>
+        <v>79634</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3299,39 +3304,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451256</v>
+        <v>451275</v>
       </c>
       <c r="R26" t="n">
-        <v>6752469</v>
+        <v>6752429</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129310404</v>
+        <v>129311235</v>
       </c>
       <c r="B34" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451456</v>
+        <v>451357</v>
       </c>
       <c r="R34" t="n">
-        <v>6752426</v>
+        <v>6752476</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129311235</v>
+        <v>129310178</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>78447</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451357</v>
+        <v>451435</v>
       </c>
       <c r="R35" t="n">
-        <v>6752476</v>
+        <v>6752354</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4363,32 +4363,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129309657</v>
+        <v>129307777</v>
       </c>
       <c r="B36" t="n">
-        <v>92831</v>
+        <v>79663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451370</v>
+        <v>451291</v>
       </c>
       <c r="R36" t="n">
-        <v>6752389</v>
+        <v>6752489</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,32 +4470,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129310178</v>
+        <v>129309657</v>
       </c>
       <c r="B37" t="n">
-        <v>78447</v>
+        <v>92832</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451435</v>
+        <v>451370</v>
       </c>
       <c r="R37" t="n">
-        <v>6752354</v>
+        <v>6752389</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4577,10 +4577,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129307777</v>
+        <v>129310404</v>
       </c>
       <c r="B38" t="n">
-        <v>79663</v>
+        <v>79634</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4612,13 +4612,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451291</v>
+        <v>451456</v>
       </c>
       <c r="R38" t="n">
-        <v>6752489</v>
+        <v>6752426</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129310637</v>
+        <v>129306645</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451442</v>
+        <v>451189</v>
       </c>
       <c r="R46" t="n">
-        <v>6752403</v>
+        <v>6752531</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,12 +5523,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5555,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129306645</v>
+        <v>129310637</v>
       </c>
       <c r="B47" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5566,21 +5561,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5590,10 +5585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451189</v>
+        <v>451442</v>
       </c>
       <c r="R47" t="n">
-        <v>6752531</v>
+        <v>6752403</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5625,7 +5620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5635,7 +5630,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5662,10 +5662,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129307334</v>
+        <v>129310466</v>
       </c>
       <c r="B48" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5673,39 +5673,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451244</v>
+        <v>451463</v>
       </c>
       <c r="R48" t="n">
-        <v>6752466</v>
+        <v>6752384</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5737,7 +5732,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5747,7 +5742,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5881,10 +5876,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129310466</v>
+        <v>129307334</v>
       </c>
       <c r="B50" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5892,34 +5887,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451463</v>
+        <v>451244</v>
       </c>
       <c r="R50" t="n">
-        <v>6752384</v>
+        <v>6752466</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5988,32 +5988,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129307240</v>
+        <v>129308051</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6023,13 +6023,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451256</v>
+        <v>451352</v>
       </c>
       <c r="R51" t="n">
-        <v>6752469</v>
+        <v>6752454</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6069,6 +6069,11 @@
       <c r="AB51" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6095,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129308409</v>
+        <v>129307728</v>
       </c>
       <c r="B52" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6106,21 +6111,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6130,13 +6135,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451275</v>
+        <v>451291</v>
       </c>
       <c r="R52" t="n">
-        <v>6752429</v>
+        <v>6752489</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6176,6 +6181,11 @@
       <c r="AB52" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6202,10 +6212,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129308051</v>
+        <v>129308409</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6213,21 +6223,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6237,13 +6247,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451352</v>
+        <v>451275</v>
       </c>
       <c r="R53" t="n">
-        <v>6752454</v>
+        <v>6752429</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6283,11 +6293,6 @@
       <c r="AB53" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6314,10 +6319,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129307728</v>
+        <v>129306533</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6325,37 +6330,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451291</v>
+        <v>451170</v>
       </c>
       <c r="R54" t="n">
-        <v>6752489</v>
+        <v>6752562</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6395,11 +6405,6 @@
       <c r="AB54" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6426,50 +6431,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129306533</v>
+        <v>129307240</v>
       </c>
       <c r="B55" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451170</v>
+        <v>451256</v>
       </c>
       <c r="R55" t="n">
-        <v>6752562</v>
+        <v>6752469</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7083,35 +7083,39 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129313806</v>
+        <v>129313901</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -7168,7 +7172,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Bild på gran, garn</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7195,39 +7199,35 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129313901</v>
+        <v>129313806</v>
       </c>
       <c r="B62" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Bild på gran, garn</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7420,7 +7420,7 @@
         <v>129309515</v>
       </c>
       <c r="B64" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129306536</v>
+        <v>129316313</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451170</v>
+        <v>451213</v>
       </c>
       <c r="R2" t="n">
-        <v>6752562</v>
+        <v>6752316</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129316313</v>
+        <v>129306536</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451213</v>
+        <v>451170</v>
       </c>
       <c r="R4" t="n">
-        <v>6752316</v>
+        <v>6752562</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129307645</v>
+        <v>129306675</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451237</v>
+        <v>451206</v>
       </c>
       <c r="R5" t="n">
-        <v>6752478</v>
+        <v>6752540</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129307362</v>
+        <v>129306875</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451244</v>
+        <v>451243</v>
       </c>
       <c r="R6" t="n">
-        <v>6752466</v>
+        <v>6752517</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129306875</v>
+        <v>129307645</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451243</v>
+        <v>451237</v>
       </c>
       <c r="R7" t="n">
-        <v>6752517</v>
+        <v>6752478</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,6 +1301,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129306675</v>
+        <v>129307362</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1362,13 +1367,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451206</v>
+        <v>451244</v>
       </c>
       <c r="R8" t="n">
-        <v>6752540</v>
+        <v>6752466</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1408,11 +1413,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2096,7 +2096,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129314017</v>
+        <v>129306457</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451253</v>
+        <v>451149</v>
       </c>
       <c r="R15" t="n">
-        <v>6752304</v>
+        <v>6752603</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,7 +2203,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129306457</v>
+        <v>129306100</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451149</v>
+        <v>451093</v>
       </c>
       <c r="R16" t="n">
-        <v>6752603</v>
+        <v>6752490</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129306100</v>
+        <v>129314017</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451093</v>
+        <v>451253</v>
       </c>
       <c r="R18" t="n">
-        <v>6752490</v>
+        <v>6752304</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3614,7 +3614,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129308422</v>
+        <v>129313973</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>451275</v>
+        <v>451258</v>
       </c>
       <c r="R29" t="n">
-        <v>6752429</v>
+        <v>6752314</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3721,7 +3721,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129306588</v>
+        <v>129308422</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>451153</v>
+        <v>451275</v>
       </c>
       <c r="R30" t="n">
-        <v>6752545</v>
+        <v>6752429</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3935,7 +3935,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129313973</v>
+        <v>129306588</v>
       </c>
       <c r="B32" t="n">
         <v>79044</v>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>451258</v>
+        <v>451153</v>
       </c>
       <c r="R32" t="n">
-        <v>6752314</v>
+        <v>6752545</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4149,32 +4149,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129311235</v>
+        <v>129309657</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451357</v>
+        <v>451370</v>
       </c>
       <c r="R34" t="n">
-        <v>6752476</v>
+        <v>6752389</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129310178</v>
+        <v>129307777</v>
       </c>
       <c r="B35" t="n">
-        <v>78447</v>
+        <v>79663</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451435</v>
+        <v>451291</v>
       </c>
       <c r="R35" t="n">
-        <v>6752354</v>
+        <v>6752489</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4363,10 +4363,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129307777</v>
+        <v>129311235</v>
       </c>
       <c r="B36" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4374,21 +4374,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451291</v>
+        <v>451357</v>
       </c>
       <c r="R36" t="n">
-        <v>6752489</v>
+        <v>6752476</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,32 +4470,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129309657</v>
+        <v>129310178</v>
       </c>
       <c r="B37" t="n">
-        <v>92832</v>
+        <v>78447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451370</v>
+        <v>451435</v>
       </c>
       <c r="R37" t="n">
-        <v>6752389</v>
+        <v>6752354</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4898,7 +4898,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129307878</v>
+        <v>129313715</v>
       </c>
       <c r="B41" t="n">
         <v>79044</v>
@@ -4933,13 +4933,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451297</v>
+        <v>451335</v>
       </c>
       <c r="R41" t="n">
-        <v>6752466</v>
+        <v>6752312</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4978,12 +4978,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5010,7 +5005,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129313715</v>
+        <v>129307878</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -5045,13 +5040,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451335</v>
+        <v>451297</v>
       </c>
       <c r="R42" t="n">
-        <v>6752312</v>
+        <v>6752466</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5080,7 +5075,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5090,7 +5085,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5229,10 +5229,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129310740</v>
+        <v>129306322</v>
       </c>
       <c r="B44" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5240,21 +5240,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>451416</v>
+        <v>451096</v>
       </c>
       <c r="R44" t="n">
-        <v>6752417</v>
+        <v>6752528</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5336,10 +5336,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129306322</v>
+        <v>129310740</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>451096</v>
+        <v>451416</v>
       </c>
       <c r="R45" t="n">
-        <v>6752528</v>
+        <v>6752417</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129306645</v>
+        <v>129310637</v>
       </c>
       <c r="B46" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451189</v>
+        <v>451442</v>
       </c>
       <c r="R46" t="n">
-        <v>6752531</v>
+        <v>6752403</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,7 +5523,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,10 +5555,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129310637</v>
+        <v>129306645</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5561,21 +5566,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5585,10 +5590,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451442</v>
+        <v>451189</v>
       </c>
       <c r="R47" t="n">
-        <v>6752403</v>
+        <v>6752531</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5620,7 +5625,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5630,12 +5635,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5769,35 +5769,40 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129307338</v>
+        <v>129307334</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -5876,40 +5881,35 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129307334</v>
+        <v>129307338</v>
       </c>
       <c r="B50" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -6538,7 +6538,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129307246</v>
+        <v>129310742</v>
       </c>
       <c r="B56" t="n">
         <v>79044</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451256</v>
+        <v>451416</v>
       </c>
       <c r="R56" t="n">
-        <v>6752469</v>
+        <v>6752417</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6645,7 +6645,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129310742</v>
+        <v>129307246</v>
       </c>
       <c r="B57" t="n">
         <v>79044</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451416</v>
+        <v>451256</v>
       </c>
       <c r="R57" t="n">
-        <v>6752417</v>
+        <v>6752469</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7083,39 +7083,35 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129313901</v>
+        <v>129313806</v>
       </c>
       <c r="B61" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -7172,7 +7168,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Bild på gran, garn</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7199,35 +7195,39 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129313806</v>
+        <v>129313901</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Bild på gran, garn</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129306675</v>
+        <v>129306875</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451206</v>
+        <v>451243</v>
       </c>
       <c r="R5" t="n">
-        <v>6752540</v>
+        <v>6752517</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,11 +1082,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129306875</v>
+        <v>129307645</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1148,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451243</v>
+        <v>451237</v>
       </c>
       <c r="R6" t="n">
-        <v>6752517</v>
+        <v>6752478</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,6 +1189,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129307645</v>
+        <v>129307362</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451237</v>
+        <v>451244</v>
       </c>
       <c r="R7" t="n">
-        <v>6752478</v>
+        <v>6752466</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,11 +1301,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129307362</v>
+        <v>129306675</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1367,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451244</v>
+        <v>451206</v>
       </c>
       <c r="R8" t="n">
-        <v>6752466</v>
+        <v>6752540</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,6 +1408,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2738,50 +2738,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129308438</v>
+        <v>129306556</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451260</v>
+        <v>451153</v>
       </c>
       <c r="R21" t="n">
-        <v>6752424</v>
+        <v>6752545</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2850,45 +2845,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129306556</v>
+        <v>129308438</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451153</v>
+        <v>451260</v>
       </c>
       <c r="R22" t="n">
-        <v>6752545</v>
+        <v>6752424</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2957,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129311305</v>
+        <v>129308406</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,21 +2968,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2992,13 +2992,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451358</v>
+        <v>451275</v>
       </c>
       <c r="R23" t="n">
-        <v>6752424</v>
+        <v>6752429</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3037,12 +3037,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,7 +3064,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129307012</v>
+        <v>129311305</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3104,10 +3099,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451262</v>
+        <v>451358</v>
       </c>
       <c r="R24" t="n">
-        <v>6752514</v>
+        <v>6752424</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3139,7 +3134,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3149,7 +3144,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3181,10 +3176,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129307237</v>
+        <v>129307012</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,42 +3187,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451256</v>
+        <v>451262</v>
       </c>
       <c r="R25" t="n">
-        <v>6752469</v>
+        <v>6752514</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3267,6 +3257,11 @@
       <c r="AB25" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3293,10 +3288,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129308406</v>
+        <v>129307237</v>
       </c>
       <c r="B26" t="n">
-        <v>79634</v>
+        <v>57724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3304,34 +3299,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451275</v>
+        <v>451256</v>
       </c>
       <c r="R26" t="n">
-        <v>6752429</v>
+        <v>6752469</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4149,32 +4149,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129309657</v>
+        <v>129310404</v>
       </c>
       <c r="B34" t="n">
-        <v>92832</v>
+        <v>79634</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451370</v>
+        <v>451456</v>
       </c>
       <c r="R34" t="n">
-        <v>6752389</v>
+        <v>6752426</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4256,32 +4256,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129307777</v>
+        <v>129309657</v>
       </c>
       <c r="B35" t="n">
-        <v>79663</v>
+        <v>92832</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451291</v>
+        <v>451370</v>
       </c>
       <c r="R35" t="n">
-        <v>6752489</v>
+        <v>6752389</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4363,10 +4363,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129311235</v>
+        <v>129307777</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4374,21 +4374,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451357</v>
+        <v>451291</v>
       </c>
       <c r="R36" t="n">
-        <v>6752476</v>
+        <v>6752489</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,10 +4470,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129310178</v>
+        <v>129311235</v>
       </c>
       <c r="B37" t="n">
-        <v>78447</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451435</v>
+        <v>451357</v>
       </c>
       <c r="R37" t="n">
-        <v>6752354</v>
+        <v>6752476</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4577,10 +4577,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129310404</v>
+        <v>129310178</v>
       </c>
       <c r="B38" t="n">
-        <v>79634</v>
+        <v>78447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451456</v>
+        <v>451435</v>
       </c>
       <c r="R38" t="n">
-        <v>6752426</v>
+        <v>6752354</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5988,32 +5988,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129308051</v>
+        <v>129307240</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6023,13 +6023,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451352</v>
+        <v>451256</v>
       </c>
       <c r="R51" t="n">
-        <v>6752454</v>
+        <v>6752469</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6069,11 +6069,6 @@
       <c r="AB51" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6100,7 +6095,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129307728</v>
+        <v>129308051</v>
       </c>
       <c r="B52" t="n">
         <v>79044</v>
@@ -6135,10 +6130,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451291</v>
+        <v>451352</v>
       </c>
       <c r="R52" t="n">
-        <v>6752489</v>
+        <v>6752454</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6212,10 +6207,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129308409</v>
+        <v>129307728</v>
       </c>
       <c r="B53" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6223,21 +6218,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6247,13 +6242,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451275</v>
+        <v>451291</v>
       </c>
       <c r="R53" t="n">
-        <v>6752429</v>
+        <v>6752489</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6293,6 +6288,11 @@
       <c r="AB53" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6319,10 +6319,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129306533</v>
+        <v>129308409</v>
       </c>
       <c r="B54" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6330,39 +6330,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451170</v>
+        <v>451275</v>
       </c>
       <c r="R54" t="n">
-        <v>6752562</v>
+        <v>6752429</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6431,45 +6426,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129307240</v>
+        <v>129306533</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451256</v>
+        <v>451170</v>
       </c>
       <c r="R55" t="n">
-        <v>6752469</v>
+        <v>6752562</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6538,10 +6538,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129310742</v>
+        <v>129309688</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6549,21 +6549,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451416</v>
+        <v>451370</v>
       </c>
       <c r="R56" t="n">
-        <v>6752417</v>
+        <v>6752389</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6645,7 +6645,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129307246</v>
+        <v>129310742</v>
       </c>
       <c r="B57" t="n">
         <v>79044</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451256</v>
+        <v>451416</v>
       </c>
       <c r="R57" t="n">
-        <v>6752469</v>
+        <v>6752417</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6752,10 +6752,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129306555</v>
+        <v>129307246</v>
       </c>
       <c r="B58" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6763,39 +6763,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451153</v>
+        <v>451256</v>
       </c>
       <c r="R58" t="n">
-        <v>6752545</v>
+        <v>6752469</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6864,10 +6859,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129309688</v>
+        <v>129306555</v>
       </c>
       <c r="B59" t="n">
-        <v>79634</v>
+        <v>57724</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6875,34 +6870,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451370</v>
+        <v>451153</v>
       </c>
       <c r="R59" t="n">
-        <v>6752389</v>
+        <v>6752545</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129316313</v>
+        <v>129309881</v>
       </c>
       <c r="B2" t="n">
         <v>79044</v>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451213</v>
+        <v>451386</v>
       </c>
       <c r="R2" t="n">
-        <v>6752316</v>
+        <v>6752391</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,6 +756,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129309881</v>
+        <v>129316313</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -817,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451386</v>
+        <v>451213</v>
       </c>
       <c r="R3" t="n">
-        <v>6752391</v>
+        <v>6752316</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,11 +868,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129306875</v>
+        <v>129307645</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451243</v>
+        <v>451237</v>
       </c>
       <c r="R5" t="n">
-        <v>6752517</v>
+        <v>6752478</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,6 +1082,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129307645</v>
+        <v>129307362</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1143,13 +1148,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451237</v>
+        <v>451244</v>
       </c>
       <c r="R6" t="n">
-        <v>6752478</v>
+        <v>6752466</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,11 +1194,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129307362</v>
+        <v>129306875</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451244</v>
+        <v>451243</v>
       </c>
       <c r="R7" t="n">
-        <v>6752466</v>
+        <v>6752517</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129306457</v>
+        <v>129314017</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451149</v>
+        <v>451253</v>
       </c>
       <c r="R15" t="n">
-        <v>6752603</v>
+        <v>6752304</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,7 +2203,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129306100</v>
+        <v>129306457</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451093</v>
+        <v>451149</v>
       </c>
       <c r="R16" t="n">
-        <v>6752490</v>
+        <v>6752603</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129314017</v>
+        <v>129306100</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451253</v>
+        <v>451093</v>
       </c>
       <c r="R18" t="n">
-        <v>6752304</v>
+        <v>6752490</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3614,7 +3614,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129313973</v>
+        <v>129308422</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>451258</v>
+        <v>451275</v>
       </c>
       <c r="R29" t="n">
-        <v>6752314</v>
+        <v>6752429</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3721,7 +3721,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129308422</v>
+        <v>129306588</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>451275</v>
+        <v>451153</v>
       </c>
       <c r="R30" t="n">
-        <v>6752429</v>
+        <v>6752545</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3935,7 +3935,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129306588</v>
+        <v>129313973</v>
       </c>
       <c r="B32" t="n">
         <v>79044</v>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>451153</v>
+        <v>451258</v>
       </c>
       <c r="R32" t="n">
-        <v>6752545</v>
+        <v>6752314</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4256,32 +4256,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129309657</v>
+        <v>129311235</v>
       </c>
       <c r="B35" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451370</v>
+        <v>451357</v>
       </c>
       <c r="R35" t="n">
-        <v>6752389</v>
+        <v>6752476</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4363,10 +4363,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129307777</v>
+        <v>129310178</v>
       </c>
       <c r="B36" t="n">
-        <v>79663</v>
+        <v>78447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4374,21 +4374,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451291</v>
+        <v>451435</v>
       </c>
       <c r="R36" t="n">
-        <v>6752489</v>
+        <v>6752354</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,10 +4470,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129311235</v>
+        <v>129307777</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451357</v>
+        <v>451291</v>
       </c>
       <c r="R37" t="n">
-        <v>6752476</v>
+        <v>6752489</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4577,32 +4577,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129310178</v>
+        <v>129309657</v>
       </c>
       <c r="B38" t="n">
-        <v>78447</v>
+        <v>92835</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451435</v>
+        <v>451370</v>
       </c>
       <c r="R38" t="n">
-        <v>6752354</v>
+        <v>6752389</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4898,7 +4898,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129313715</v>
+        <v>129307878</v>
       </c>
       <c r="B41" t="n">
         <v>79044</v>
@@ -4933,13 +4933,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451335</v>
+        <v>451297</v>
       </c>
       <c r="R41" t="n">
-        <v>6752312</v>
+        <v>6752466</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4978,7 +4978,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5005,7 +5010,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129307878</v>
+        <v>129313715</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -5040,13 +5045,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451297</v>
+        <v>451335</v>
       </c>
       <c r="R42" t="n">
-        <v>6752466</v>
+        <v>6752312</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5075,7 +5080,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5085,12 +5090,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5229,10 +5229,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129306322</v>
+        <v>129310740</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5240,21 +5240,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>451096</v>
+        <v>451416</v>
       </c>
       <c r="R44" t="n">
-        <v>6752528</v>
+        <v>6752417</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5336,10 +5336,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129310740</v>
+        <v>129306322</v>
       </c>
       <c r="B45" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>451416</v>
+        <v>451096</v>
       </c>
       <c r="R45" t="n">
-        <v>6752417</v>
+        <v>6752528</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129310637</v>
+        <v>129306645</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451442</v>
+        <v>451189</v>
       </c>
       <c r="R46" t="n">
-        <v>6752403</v>
+        <v>6752531</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,12 +5523,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5555,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129306645</v>
+        <v>129310637</v>
       </c>
       <c r="B47" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5566,21 +5561,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5590,10 +5585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451189</v>
+        <v>451442</v>
       </c>
       <c r="R47" t="n">
-        <v>6752531</v>
+        <v>6752403</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5625,7 +5620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5635,7 +5630,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5988,32 +5988,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129307240</v>
+        <v>129308051</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6023,13 +6023,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451256</v>
+        <v>451352</v>
       </c>
       <c r="R51" t="n">
-        <v>6752469</v>
+        <v>6752454</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6069,6 +6069,11 @@
       <c r="AB51" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6095,7 +6100,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129308051</v>
+        <v>129307728</v>
       </c>
       <c r="B52" t="n">
         <v>79044</v>
@@ -6130,10 +6135,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451352</v>
+        <v>451291</v>
       </c>
       <c r="R52" t="n">
-        <v>6752454</v>
+        <v>6752489</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6207,10 +6212,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129307728</v>
+        <v>129308409</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6218,21 +6223,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6242,13 +6247,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451291</v>
+        <v>451275</v>
       </c>
       <c r="R53" t="n">
-        <v>6752489</v>
+        <v>6752429</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6288,11 +6293,6 @@
       <c r="AB53" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6319,32 +6319,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129308409</v>
+        <v>129307240</v>
       </c>
       <c r="B54" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6354,10 +6354,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451275</v>
+        <v>451256</v>
       </c>
       <c r="R54" t="n">
-        <v>6752429</v>
+        <v>6752469</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6538,10 +6538,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129309688</v>
+        <v>129307246</v>
       </c>
       <c r="B56" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6549,21 +6549,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451370</v>
+        <v>451256</v>
       </c>
       <c r="R56" t="n">
-        <v>6752389</v>
+        <v>6752469</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6752,10 +6752,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129307246</v>
+        <v>129306555</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6763,34 +6763,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451256</v>
+        <v>451153</v>
       </c>
       <c r="R58" t="n">
-        <v>6752469</v>
+        <v>6752545</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6859,10 +6864,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129306555</v>
+        <v>129309688</v>
       </c>
       <c r="B59" t="n">
-        <v>57724</v>
+        <v>79634</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6870,39 +6875,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451153</v>
+        <v>451370</v>
       </c>
       <c r="R59" t="n">
-        <v>6752545</v>
+        <v>6752389</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7198,7 +7198,7 @@
         <v>129313901</v>
       </c>
       <c r="B62" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>129309515</v>
       </c>
       <c r="B64" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129307645</v>
+        <v>129306875</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451237</v>
+        <v>451243</v>
       </c>
       <c r="R5" t="n">
-        <v>6752478</v>
+        <v>6752517</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,11 +1082,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129307362</v>
+        <v>129306675</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1148,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451244</v>
+        <v>451206</v>
       </c>
       <c r="R6" t="n">
-        <v>6752466</v>
+        <v>6752540</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,6 +1189,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129306875</v>
+        <v>129307645</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451243</v>
+        <v>451237</v>
       </c>
       <c r="R7" t="n">
-        <v>6752517</v>
+        <v>6752478</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,6 +1301,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129306675</v>
+        <v>129307362</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1362,13 +1367,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451206</v>
+        <v>451244</v>
       </c>
       <c r="R8" t="n">
-        <v>6752540</v>
+        <v>6752466</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1408,11 +1413,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129306575</v>
+        <v>129307805</v>
       </c>
       <c r="B10" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451153</v>
+        <v>451335</v>
       </c>
       <c r="R10" t="n">
-        <v>6752545</v>
+        <v>6752504</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129312692</v>
+        <v>129307040</v>
       </c>
       <c r="B11" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,37 +1669,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451369</v>
+        <v>451262</v>
       </c>
       <c r="R11" t="n">
-        <v>6752313</v>
+        <v>6752514</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1723,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129307805</v>
+        <v>129306575</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,39 +1781,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451335</v>
+        <v>451153</v>
       </c>
       <c r="R12" t="n">
-        <v>6752504</v>
+        <v>6752545</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129307040</v>
+        <v>129312692</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,42 +1888,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451262</v>
+        <v>451369</v>
       </c>
       <c r="R13" t="n">
-        <v>6752514</v>
+        <v>6752313</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2957,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129308406</v>
+        <v>129307237</v>
       </c>
       <c r="B23" t="n">
-        <v>79634</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,34 +2968,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451275</v>
+        <v>451256</v>
       </c>
       <c r="R23" t="n">
-        <v>6752429</v>
+        <v>6752469</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3288,10 +3293,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129307237</v>
+        <v>129308406</v>
       </c>
       <c r="B26" t="n">
-        <v>57724</v>
+        <v>79634</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3299,39 +3304,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451256</v>
+        <v>451275</v>
       </c>
       <c r="R26" t="n">
-        <v>6752469</v>
+        <v>6752429</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4149,32 +4149,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129310404</v>
+        <v>129309657</v>
       </c>
       <c r="B34" t="n">
-        <v>79634</v>
+        <v>92835</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451456</v>
+        <v>451370</v>
       </c>
       <c r="R34" t="n">
-        <v>6752426</v>
+        <v>6752389</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4577,32 +4577,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129309657</v>
+        <v>129310404</v>
       </c>
       <c r="B38" t="n">
-        <v>92835</v>
+        <v>79634</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451370</v>
+        <v>451456</v>
       </c>
       <c r="R38" t="n">
-        <v>6752389</v>
+        <v>6752426</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5662,10 +5662,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129310466</v>
+        <v>129307334</v>
       </c>
       <c r="B48" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5673,34 +5673,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451463</v>
+        <v>451244</v>
       </c>
       <c r="R48" t="n">
-        <v>6752384</v>
+        <v>6752466</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5732,7 +5737,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5742,7 +5747,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5769,40 +5774,35 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129307334</v>
+        <v>129307338</v>
       </c>
       <c r="B49" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -5881,32 +5881,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129307338</v>
+        <v>129310466</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451244</v>
+        <v>451463</v>
       </c>
       <c r="R50" t="n">
-        <v>6752466</v>
+        <v>6752384</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6645,10 +6645,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129310742</v>
+        <v>129309688</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6656,21 +6656,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451416</v>
+        <v>451370</v>
       </c>
       <c r="R57" t="n">
-        <v>6752417</v>
+        <v>6752389</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6752,10 +6752,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129306555</v>
+        <v>129310742</v>
       </c>
       <c r="B58" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6763,39 +6763,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451153</v>
+        <v>451416</v>
       </c>
       <c r="R58" t="n">
-        <v>6752545</v>
+        <v>6752417</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6827,7 +6822,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6837,7 +6832,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6864,10 +6859,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129309688</v>
+        <v>129306555</v>
       </c>
       <c r="B59" t="n">
-        <v>79634</v>
+        <v>57724</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6875,34 +6870,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451370</v>
+        <v>451153</v>
       </c>
       <c r="R59" t="n">
-        <v>6752389</v>
+        <v>6752545</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129306875</v>
+        <v>129307645</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451243</v>
+        <v>451237</v>
       </c>
       <c r="R5" t="n">
-        <v>6752517</v>
+        <v>6752478</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,6 +1082,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129306675</v>
+        <v>129307362</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1143,13 +1148,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451206</v>
+        <v>451244</v>
       </c>
       <c r="R6" t="n">
-        <v>6752540</v>
+        <v>6752466</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,11 +1194,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129307645</v>
+        <v>129306875</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451237</v>
+        <v>451243</v>
       </c>
       <c r="R7" t="n">
-        <v>6752478</v>
+        <v>6752517</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,11 +1301,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129307362</v>
+        <v>129306675</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1367,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451244</v>
+        <v>451206</v>
       </c>
       <c r="R8" t="n">
-        <v>6752466</v>
+        <v>6752540</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,6 +1408,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129307805</v>
+        <v>129306575</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,39 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451335</v>
+        <v>451153</v>
       </c>
       <c r="R10" t="n">
-        <v>6752504</v>
+        <v>6752545</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129307040</v>
+        <v>129312692</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,42 +1664,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451262</v>
+        <v>451369</v>
       </c>
       <c r="R11" t="n">
-        <v>6752514</v>
+        <v>6752313</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129306575</v>
+        <v>129307805</v>
       </c>
       <c r="B12" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,34 +1771,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451153</v>
+        <v>451335</v>
       </c>
       <c r="R12" t="n">
-        <v>6752545</v>
+        <v>6752504</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129312692</v>
+        <v>129307040</v>
       </c>
       <c r="B13" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,37 +1883,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451369</v>
+        <v>451262</v>
       </c>
       <c r="R13" t="n">
-        <v>6752313</v>
+        <v>6752514</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,32 +2096,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129314017</v>
+        <v>129307042</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,13 +2131,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451253</v>
+        <v>451262</v>
       </c>
       <c r="R15" t="n">
-        <v>6752304</v>
+        <v>6752514</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,7 +2203,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129306457</v>
+        <v>129314017</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451149</v>
+        <v>451253</v>
       </c>
       <c r="R16" t="n">
-        <v>6752603</v>
+        <v>6752304</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,7 +2310,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129306554</v>
+        <v>129306457</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451170</v>
+        <v>451149</v>
       </c>
       <c r="R17" t="n">
-        <v>6752562</v>
+        <v>6752603</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129306100</v>
+        <v>129306554</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451093</v>
+        <v>451170</v>
       </c>
       <c r="R18" t="n">
-        <v>6752490</v>
+        <v>6752562</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2524,32 +2524,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129307042</v>
+        <v>129306100</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,13 +2559,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451262</v>
+        <v>451093</v>
       </c>
       <c r="R19" t="n">
-        <v>6752514</v>
+        <v>6752490</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2631,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129306511</v>
+        <v>129308438</v>
       </c>
       <c r="B20" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,34 +2642,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451170</v>
+        <v>451260</v>
       </c>
       <c r="R20" t="n">
-        <v>6752562</v>
+        <v>6752424</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,32 +2743,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129306556</v>
+        <v>129306511</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2773,10 +2778,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451153</v>
+        <v>451170</v>
       </c>
       <c r="R21" t="n">
-        <v>6752545</v>
+        <v>6752562</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2845,50 +2850,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129308438</v>
+        <v>129306556</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451260</v>
+        <v>451153</v>
       </c>
       <c r="R22" t="n">
-        <v>6752424</v>
+        <v>6752545</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3069,10 +3069,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129311305</v>
+        <v>129308406</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,21 +3080,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3104,13 +3104,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451358</v>
+        <v>451275</v>
       </c>
       <c r="R24" t="n">
-        <v>6752424</v>
+        <v>6752429</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3149,12 +3149,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3181,7 +3176,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129307012</v>
+        <v>129311305</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3216,10 +3211,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451262</v>
+        <v>451358</v>
       </c>
       <c r="R25" t="n">
-        <v>6752514</v>
+        <v>6752424</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3251,7 +3246,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3261,7 +3256,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3293,10 +3288,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129308406</v>
+        <v>129307012</v>
       </c>
       <c r="B26" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3304,21 +3299,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3328,13 +3323,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451275</v>
+        <v>451262</v>
       </c>
       <c r="R26" t="n">
-        <v>6752429</v>
+        <v>6752514</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3374,6 +3369,11 @@
       <c r="AB26" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -5229,10 +5229,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129310740</v>
+        <v>129306322</v>
       </c>
       <c r="B44" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5240,21 +5240,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>451416</v>
+        <v>451096</v>
       </c>
       <c r="R44" t="n">
-        <v>6752417</v>
+        <v>6752528</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5336,10 +5336,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129306322</v>
+        <v>129310740</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>451096</v>
+        <v>451416</v>
       </c>
       <c r="R45" t="n">
-        <v>6752528</v>
+        <v>6752417</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129306645</v>
+        <v>129310637</v>
       </c>
       <c r="B46" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451189</v>
+        <v>451442</v>
       </c>
       <c r="R46" t="n">
-        <v>6752531</v>
+        <v>6752403</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,7 +5523,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,10 +5555,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129310637</v>
+        <v>129306645</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5561,21 +5566,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5585,10 +5590,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451442</v>
+        <v>451189</v>
       </c>
       <c r="R47" t="n">
-        <v>6752403</v>
+        <v>6752531</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5620,7 +5625,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5630,12 +5635,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5662,10 +5662,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129307334</v>
+        <v>129310466</v>
       </c>
       <c r="B48" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5673,39 +5673,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451244</v>
+        <v>451463</v>
       </c>
       <c r="R48" t="n">
-        <v>6752466</v>
+        <v>6752384</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5737,7 +5732,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5747,7 +5742,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5774,35 +5769,40 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129307338</v>
+        <v>129307334</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -5881,32 +5881,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129310466</v>
+        <v>129307338</v>
       </c>
       <c r="B50" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451463</v>
+        <v>451244</v>
       </c>
       <c r="R50" t="n">
-        <v>6752384</v>
+        <v>6752466</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6319,45 +6319,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129307240</v>
+        <v>129306533</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451256</v>
+        <v>451170</v>
       </c>
       <c r="R54" t="n">
-        <v>6752469</v>
+        <v>6752562</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6426,50 +6431,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129306533</v>
+        <v>129307240</v>
       </c>
       <c r="B55" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451170</v>
+        <v>451256</v>
       </c>
       <c r="R55" t="n">
-        <v>6752562</v>
+        <v>6752469</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6538,10 +6538,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129307246</v>
+        <v>129309688</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6549,21 +6549,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451256</v>
+        <v>451370</v>
       </c>
       <c r="R56" t="n">
-        <v>6752469</v>
+        <v>6752389</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6645,10 +6645,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129309688</v>
+        <v>129306555</v>
       </c>
       <c r="B57" t="n">
-        <v>79634</v>
+        <v>57724</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6656,34 +6656,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451370</v>
+        <v>451153</v>
       </c>
       <c r="R57" t="n">
-        <v>6752389</v>
+        <v>6752545</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6715,7 +6720,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6725,7 +6730,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6752,7 +6757,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129310742</v>
+        <v>129307246</v>
       </c>
       <c r="B58" t="n">
         <v>79044</v>
@@ -6787,10 +6792,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451416</v>
+        <v>451256</v>
       </c>
       <c r="R58" t="n">
-        <v>6752417</v>
+        <v>6752469</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6822,7 +6827,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6832,7 +6837,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6859,10 +6864,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129306555</v>
+        <v>129310742</v>
       </c>
       <c r="B59" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6870,39 +6875,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451153</v>
+        <v>451416</v>
       </c>
       <c r="R59" t="n">
-        <v>6752545</v>
+        <v>6752417</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129306575</v>
+        <v>129307805</v>
       </c>
       <c r="B10" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451153</v>
+        <v>451335</v>
       </c>
       <c r="R10" t="n">
-        <v>6752545</v>
+        <v>6752504</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129312692</v>
+        <v>129307040</v>
       </c>
       <c r="B11" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,37 +1669,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451369</v>
+        <v>451262</v>
       </c>
       <c r="R11" t="n">
-        <v>6752313</v>
+        <v>6752514</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1723,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129307805</v>
+        <v>129306575</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,39 +1781,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451335</v>
+        <v>451153</v>
       </c>
       <c r="R12" t="n">
-        <v>6752504</v>
+        <v>6752545</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129307040</v>
+        <v>129312692</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,42 +1888,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451262</v>
+        <v>451369</v>
       </c>
       <c r="R13" t="n">
-        <v>6752514</v>
+        <v>6752313</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,32 +2096,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129307042</v>
+        <v>129314017</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,13 +2131,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451262</v>
+        <v>451253</v>
       </c>
       <c r="R15" t="n">
-        <v>6752514</v>
+        <v>6752304</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,7 +2203,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129314017</v>
+        <v>129306457</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451253</v>
+        <v>451149</v>
       </c>
       <c r="R16" t="n">
-        <v>6752304</v>
+        <v>6752603</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,7 +2310,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129306457</v>
+        <v>129306554</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451149</v>
+        <v>451170</v>
       </c>
       <c r="R17" t="n">
-        <v>6752603</v>
+        <v>6752562</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129306554</v>
+        <v>129306100</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451170</v>
+        <v>451093</v>
       </c>
       <c r="R18" t="n">
-        <v>6752562</v>
+        <v>6752490</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2524,32 +2524,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129306100</v>
+        <v>129307042</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,13 +2559,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451093</v>
+        <v>451262</v>
       </c>
       <c r="R19" t="n">
-        <v>6752490</v>
+        <v>6752514</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2957,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129307237</v>
+        <v>129308406</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>79634</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,39 +2968,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451256</v>
+        <v>451275</v>
       </c>
       <c r="R23" t="n">
-        <v>6752469</v>
+        <v>6752429</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3069,10 +3064,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129308406</v>
+        <v>129307237</v>
       </c>
       <c r="B24" t="n">
-        <v>79634</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,34 +3075,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451275</v>
+        <v>451256</v>
       </c>
       <c r="R24" t="n">
-        <v>6752429</v>
+        <v>6752469</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -4149,32 +4149,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129309657</v>
+        <v>129310404</v>
       </c>
       <c r="B34" t="n">
-        <v>92835</v>
+        <v>79634</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451370</v>
+        <v>451456</v>
       </c>
       <c r="R34" t="n">
-        <v>6752389</v>
+        <v>6752426</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4256,32 +4256,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129311235</v>
+        <v>129309657</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451357</v>
+        <v>451370</v>
       </c>
       <c r="R35" t="n">
-        <v>6752476</v>
+        <v>6752389</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4363,10 +4363,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129310178</v>
+        <v>129307777</v>
       </c>
       <c r="B36" t="n">
-        <v>78447</v>
+        <v>79663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4374,21 +4374,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451435</v>
+        <v>451291</v>
       </c>
       <c r="R36" t="n">
-        <v>6752354</v>
+        <v>6752489</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,10 +4470,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129307777</v>
+        <v>129311235</v>
       </c>
       <c r="B37" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451291</v>
+        <v>451357</v>
       </c>
       <c r="R37" t="n">
-        <v>6752489</v>
+        <v>6752476</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4577,10 +4577,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129310404</v>
+        <v>129310178</v>
       </c>
       <c r="B38" t="n">
-        <v>79634</v>
+        <v>78447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451456</v>
+        <v>451435</v>
       </c>
       <c r="R38" t="n">
-        <v>6752426</v>
+        <v>6752354</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5769,40 +5769,35 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129307334</v>
+        <v>129307338</v>
       </c>
       <c r="B49" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -5881,35 +5876,40 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129307338</v>
+        <v>129307334</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -5988,32 +5988,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129308051</v>
+        <v>129307240</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6023,13 +6023,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451352</v>
+        <v>451256</v>
       </c>
       <c r="R51" t="n">
-        <v>6752454</v>
+        <v>6752469</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6069,11 +6069,6 @@
       <c r="AB51" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6100,7 +6095,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129307728</v>
+        <v>129308051</v>
       </c>
       <c r="B52" t="n">
         <v>79044</v>
@@ -6135,10 +6130,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451291</v>
+        <v>451352</v>
       </c>
       <c r="R52" t="n">
-        <v>6752489</v>
+        <v>6752454</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6212,10 +6207,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129308409</v>
+        <v>129307728</v>
       </c>
       <c r="B53" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6223,21 +6218,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6247,13 +6242,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451275</v>
+        <v>451291</v>
       </c>
       <c r="R53" t="n">
-        <v>6752429</v>
+        <v>6752489</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6293,6 +6288,11 @@
       <c r="AB53" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6431,32 +6431,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129307240</v>
+        <v>129308409</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6466,10 +6466,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451256</v>
+        <v>451275</v>
       </c>
       <c r="R55" t="n">
-        <v>6752469</v>
+        <v>6752429</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6538,10 +6538,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129309688</v>
+        <v>129306555</v>
       </c>
       <c r="B56" t="n">
-        <v>79634</v>
+        <v>57724</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6549,34 +6549,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451370</v>
+        <v>451153</v>
       </c>
       <c r="R56" t="n">
-        <v>6752389</v>
+        <v>6752545</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6608,7 +6613,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6618,7 +6623,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6645,10 +6650,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129306555</v>
+        <v>129307246</v>
       </c>
       <c r="B57" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6656,39 +6661,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451153</v>
+        <v>451256</v>
       </c>
       <c r="R57" t="n">
-        <v>6752545</v>
+        <v>6752469</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6757,7 +6757,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129307246</v>
+        <v>129310742</v>
       </c>
       <c r="B58" t="n">
         <v>79044</v>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451256</v>
+        <v>451416</v>
       </c>
       <c r="R58" t="n">
-        <v>6752469</v>
+        <v>6752417</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6864,10 +6864,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129310742</v>
+        <v>129309688</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6875,21 +6875,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451416</v>
+        <v>451370</v>
       </c>
       <c r="R59" t="n">
-        <v>6752417</v>
+        <v>6752389</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -1770,7 +1770,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129306575</v>
+        <v>129312692</v>
       </c>
       <c r="B12" t="n">
         <v>79663</v>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451153</v>
+        <v>451369</v>
       </c>
       <c r="R12" t="n">
-        <v>6752545</v>
+        <v>6752313</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,7 +1877,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129312692</v>
+        <v>129306575</v>
       </c>
       <c r="B13" t="n">
         <v>79663</v>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451369</v>
+        <v>451153</v>
       </c>
       <c r="R13" t="n">
-        <v>6752313</v>
+        <v>6752545</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2631,50 +2631,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129308438</v>
+        <v>129306556</v>
       </c>
       <c r="B20" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451260</v>
+        <v>451153</v>
       </c>
       <c r="R20" t="n">
-        <v>6752424</v>
+        <v>6752545</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2850,45 +2845,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129306556</v>
+        <v>129308438</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451153</v>
+        <v>451260</v>
       </c>
       <c r="R22" t="n">
-        <v>6752545</v>
+        <v>6752424</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3064,10 +3064,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129307237</v>
+        <v>129311305</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,42 +3075,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451256</v>
+        <v>451358</v>
       </c>
       <c r="R24" t="n">
-        <v>6752469</v>
+        <v>6752424</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3139,7 +3134,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3149,7 +3144,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3176,7 +3176,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129311305</v>
+        <v>129307012</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451358</v>
+        <v>451262</v>
       </c>
       <c r="R25" t="n">
-        <v>6752424</v>
+        <v>6752514</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3288,10 +3288,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129307012</v>
+        <v>129307237</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3299,37 +3299,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451262</v>
+        <v>451256</v>
       </c>
       <c r="R26" t="n">
-        <v>6752514</v>
+        <v>6752469</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3369,11 +3374,6 @@
       <c r="AB26" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3614,10 +3614,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129308422</v>
+        <v>129314054</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,21 +3625,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>451275</v>
+        <v>451213</v>
       </c>
       <c r="R29" t="n">
-        <v>6752429</v>
+        <v>6752316</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3721,7 +3721,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129306588</v>
+        <v>129308422</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>451153</v>
+        <v>451275</v>
       </c>
       <c r="R30" t="n">
-        <v>6752545</v>
+        <v>6752429</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129306615</v>
+        <v>129306588</v>
       </c>
       <c r="B31" t="n">
         <v>79044</v>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>451164</v>
+        <v>451153</v>
       </c>
       <c r="R31" t="n">
-        <v>6752537</v>
+        <v>6752545</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3935,7 +3935,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129313973</v>
+        <v>129306615</v>
       </c>
       <c r="B32" t="n">
         <v>79044</v>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>451258</v>
+        <v>451164</v>
       </c>
       <c r="R32" t="n">
-        <v>6752314</v>
+        <v>6752537</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4042,10 +4042,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129314054</v>
+        <v>129313973</v>
       </c>
       <c r="B33" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4053,21 +4053,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>451213</v>
+        <v>451258</v>
       </c>
       <c r="R33" t="n">
-        <v>6752316</v>
+        <v>6752314</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129310404</v>
+        <v>129307777</v>
       </c>
       <c r="B34" t="n">
-        <v>79634</v>
+        <v>79663</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4184,13 +4184,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451456</v>
+        <v>451291</v>
       </c>
       <c r="R34" t="n">
-        <v>6752426</v>
+        <v>6752489</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4256,32 +4256,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129309657</v>
+        <v>129310178</v>
       </c>
       <c r="B35" t="n">
-        <v>92835</v>
+        <v>78447</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451370</v>
+        <v>451435</v>
       </c>
       <c r="R35" t="n">
-        <v>6752389</v>
+        <v>6752354</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4363,32 +4363,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129307777</v>
+        <v>129309657</v>
       </c>
       <c r="B36" t="n">
-        <v>79663</v>
+        <v>92835</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451291</v>
+        <v>451370</v>
       </c>
       <c r="R36" t="n">
-        <v>6752489</v>
+        <v>6752389</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4577,10 +4577,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129310178</v>
+        <v>129310404</v>
       </c>
       <c r="B38" t="n">
-        <v>78447</v>
+        <v>79634</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451435</v>
+        <v>451456</v>
       </c>
       <c r="R38" t="n">
-        <v>6752354</v>
+        <v>6752426</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5662,10 +5662,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129310466</v>
+        <v>129307334</v>
       </c>
       <c r="B48" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5673,34 +5673,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451463</v>
+        <v>451244</v>
       </c>
       <c r="R48" t="n">
-        <v>6752384</v>
+        <v>6752466</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5732,7 +5737,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5742,7 +5747,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5876,10 +5881,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129307334</v>
+        <v>129310466</v>
       </c>
       <c r="B50" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5887,39 +5892,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451244</v>
+        <v>451463</v>
       </c>
       <c r="R50" t="n">
-        <v>6752466</v>
+        <v>6752384</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5988,32 +5988,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129307240</v>
+        <v>129308409</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6023,10 +6023,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451256</v>
+        <v>451275</v>
       </c>
       <c r="R51" t="n">
-        <v>6752469</v>
+        <v>6752429</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6431,32 +6431,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129308409</v>
+        <v>129307240</v>
       </c>
       <c r="B55" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6466,10 +6466,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451275</v>
+        <v>451256</v>
       </c>
       <c r="R55" t="n">
-        <v>6752429</v>
+        <v>6752469</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129307645</v>
+        <v>129306869</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451237</v>
+        <v>451243</v>
       </c>
       <c r="R5" t="n">
-        <v>6752478</v>
+        <v>6752517</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,11 +1082,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129307362</v>
+        <v>129307645</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1148,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451244</v>
+        <v>451237</v>
       </c>
       <c r="R6" t="n">
-        <v>6752466</v>
+        <v>6752478</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,6 +1189,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129306875</v>
+        <v>129307362</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451243</v>
+        <v>451244</v>
       </c>
       <c r="R7" t="n">
-        <v>6752517</v>
+        <v>6752466</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129306675</v>
+        <v>129306875</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451206</v>
+        <v>451243</v>
       </c>
       <c r="R8" t="n">
-        <v>6752540</v>
+        <v>6752517</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1408,11 +1408,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129306869</v>
+        <v>129306675</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,13 +1469,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451243</v>
+        <v>451206</v>
       </c>
       <c r="R9" t="n">
-        <v>6752517</v>
+        <v>6752540</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1520,6 +1515,11 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129307805</v>
+        <v>129306575</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,39 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451335</v>
+        <v>451153</v>
       </c>
       <c r="R10" t="n">
-        <v>6752504</v>
+        <v>6752545</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129307040</v>
+        <v>129312692</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,42 +1664,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451262</v>
+        <v>451369</v>
       </c>
       <c r="R11" t="n">
-        <v>6752514</v>
+        <v>6752313</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129312692</v>
+        <v>129307805</v>
       </c>
       <c r="B12" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,34 +1771,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451369</v>
+        <v>451335</v>
       </c>
       <c r="R12" t="n">
-        <v>6752313</v>
+        <v>6752504</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1850,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129306575</v>
+        <v>129307040</v>
       </c>
       <c r="B13" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,37 +1883,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451153</v>
+        <v>451262</v>
       </c>
       <c r="R13" t="n">
-        <v>6752545</v>
+        <v>6752514</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2096,32 +2096,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129314017</v>
+        <v>129307042</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,13 +2131,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451253</v>
+        <v>451262</v>
       </c>
       <c r="R15" t="n">
-        <v>6752304</v>
+        <v>6752514</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,7 +2203,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129306457</v>
+        <v>129314017</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451149</v>
+        <v>451253</v>
       </c>
       <c r="R16" t="n">
-        <v>6752603</v>
+        <v>6752304</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,7 +2310,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129306554</v>
+        <v>129306457</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451170</v>
+        <v>451149</v>
       </c>
       <c r="R17" t="n">
-        <v>6752562</v>
+        <v>6752603</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129306100</v>
+        <v>129306554</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451093</v>
+        <v>451170</v>
       </c>
       <c r="R18" t="n">
-        <v>6752490</v>
+        <v>6752562</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2524,32 +2524,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129307042</v>
+        <v>129306100</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,13 +2559,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451262</v>
+        <v>451093</v>
       </c>
       <c r="R19" t="n">
-        <v>6752514</v>
+        <v>6752490</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2631,32 +2631,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129306556</v>
+        <v>129306511</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451153</v>
+        <v>451170</v>
       </c>
       <c r="R20" t="n">
-        <v>6752545</v>
+        <v>6752562</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129306511</v>
+        <v>129308438</v>
       </c>
       <c r="B21" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2749,34 +2749,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451170</v>
+        <v>451260</v>
       </c>
       <c r="R21" t="n">
-        <v>6752562</v>
+        <v>6752424</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2845,50 +2850,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129308438</v>
+        <v>129306556</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451260</v>
+        <v>451153</v>
       </c>
       <c r="R22" t="n">
-        <v>6752424</v>
+        <v>6752545</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2957,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129308406</v>
+        <v>129307237</v>
       </c>
       <c r="B23" t="n">
-        <v>79634</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,34 +2968,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451275</v>
+        <v>451256</v>
       </c>
       <c r="R23" t="n">
-        <v>6752429</v>
+        <v>6752469</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3064,10 +3069,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129311305</v>
+        <v>129308406</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,21 +3080,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3099,13 +3104,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451358</v>
+        <v>451275</v>
       </c>
       <c r="R24" t="n">
-        <v>6752424</v>
+        <v>6752429</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3134,7 +3139,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3144,12 +3149,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3176,7 +3176,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129307012</v>
+        <v>129311305</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451262</v>
+        <v>451358</v>
       </c>
       <c r="R25" t="n">
-        <v>6752514</v>
+        <v>6752424</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3288,10 +3288,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129307237</v>
+        <v>129307012</v>
       </c>
       <c r="B26" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3299,42 +3299,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451256</v>
+        <v>451262</v>
       </c>
       <c r="R26" t="n">
-        <v>6752469</v>
+        <v>6752514</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3374,6 +3369,11 @@
       <c r="AB26" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3614,10 +3614,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129314054</v>
+        <v>129308422</v>
       </c>
       <c r="B29" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,21 +3625,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>451213</v>
+        <v>451275</v>
       </c>
       <c r="R29" t="n">
-        <v>6752316</v>
+        <v>6752429</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3721,7 +3721,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129308422</v>
+        <v>129306588</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>451275</v>
+        <v>451153</v>
       </c>
       <c r="R30" t="n">
-        <v>6752429</v>
+        <v>6752545</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129306588</v>
+        <v>129306615</v>
       </c>
       <c r="B31" t="n">
         <v>79044</v>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>451153</v>
+        <v>451164</v>
       </c>
       <c r="R31" t="n">
-        <v>6752545</v>
+        <v>6752537</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3935,7 +3935,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129306615</v>
+        <v>129313973</v>
       </c>
       <c r="B32" t="n">
         <v>79044</v>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>451164</v>
+        <v>451258</v>
       </c>
       <c r="R32" t="n">
-        <v>6752537</v>
+        <v>6752314</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4042,10 +4042,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129313973</v>
+        <v>129314054</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4053,21 +4053,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>451258</v>
+        <v>451213</v>
       </c>
       <c r="R33" t="n">
-        <v>6752314</v>
+        <v>6752316</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4149,32 +4149,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129307777</v>
+        <v>129309657</v>
       </c>
       <c r="B34" t="n">
-        <v>79663</v>
+        <v>92835</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4184,13 +4184,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451291</v>
+        <v>451370</v>
       </c>
       <c r="R34" t="n">
-        <v>6752489</v>
+        <v>6752389</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4256,10 +4256,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129310178</v>
+        <v>129311235</v>
       </c>
       <c r="B35" t="n">
-        <v>78447</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451435</v>
+        <v>451357</v>
       </c>
       <c r="R35" t="n">
-        <v>6752354</v>
+        <v>6752476</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4363,32 +4363,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129309657</v>
+        <v>129310178</v>
       </c>
       <c r="B36" t="n">
-        <v>92835</v>
+        <v>78447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451370</v>
+        <v>451435</v>
       </c>
       <c r="R36" t="n">
-        <v>6752389</v>
+        <v>6752354</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4470,10 +4470,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129311235</v>
+        <v>129307777</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451357</v>
+        <v>451291</v>
       </c>
       <c r="R37" t="n">
-        <v>6752476</v>
+        <v>6752489</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5229,10 +5229,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129306322</v>
+        <v>129310740</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5240,21 +5240,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>451096</v>
+        <v>451416</v>
       </c>
       <c r="R44" t="n">
-        <v>6752528</v>
+        <v>6752417</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5336,10 +5336,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129310740</v>
+        <v>129306322</v>
       </c>
       <c r="B45" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>451416</v>
+        <v>451096</v>
       </c>
       <c r="R45" t="n">
-        <v>6752417</v>
+        <v>6752528</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129310637</v>
+        <v>129306645</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451442</v>
+        <v>451189</v>
       </c>
       <c r="R46" t="n">
-        <v>6752403</v>
+        <v>6752531</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,12 +5523,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5555,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129306645</v>
+        <v>129310637</v>
       </c>
       <c r="B47" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5566,21 +5561,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5590,10 +5585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451189</v>
+        <v>451442</v>
       </c>
       <c r="R47" t="n">
-        <v>6752531</v>
+        <v>6752403</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5625,7 +5620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5635,7 +5630,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5662,40 +5662,35 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129307334</v>
+        <v>129307338</v>
       </c>
       <c r="B48" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -5774,32 +5769,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129307338</v>
+        <v>129310466</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5809,10 +5804,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>451244</v>
+        <v>451463</v>
       </c>
       <c r="R49" t="n">
-        <v>6752466</v>
+        <v>6752384</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5844,7 +5839,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5854,7 +5849,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5881,10 +5876,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129310466</v>
+        <v>129307334</v>
       </c>
       <c r="B50" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5892,34 +5887,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451463</v>
+        <v>451244</v>
       </c>
       <c r="R50" t="n">
-        <v>6752384</v>
+        <v>6752466</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5988,10 +5988,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129308409</v>
+        <v>129306533</v>
       </c>
       <c r="B51" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5999,34 +5999,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451275</v>
+        <v>451170</v>
       </c>
       <c r="R51" t="n">
-        <v>6752429</v>
+        <v>6752562</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6319,10 +6324,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129306533</v>
+        <v>129308409</v>
       </c>
       <c r="B54" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6330,39 +6335,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451170</v>
+        <v>451275</v>
       </c>
       <c r="R54" t="n">
-        <v>6752562</v>
+        <v>6752429</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6538,10 +6538,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129306555</v>
+        <v>129307246</v>
       </c>
       <c r="B56" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6549,39 +6549,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451153</v>
+        <v>451256</v>
       </c>
       <c r="R56" t="n">
-        <v>6752545</v>
+        <v>6752469</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6650,7 +6645,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129307246</v>
+        <v>129310742</v>
       </c>
       <c r="B57" t="n">
         <v>79044</v>
@@ -6685,10 +6680,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451256</v>
+        <v>451416</v>
       </c>
       <c r="R57" t="n">
-        <v>6752469</v>
+        <v>6752417</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6720,7 +6715,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6730,7 +6725,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6757,10 +6752,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129310742</v>
+        <v>129306555</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6768,34 +6763,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451416</v>
+        <v>451153</v>
       </c>
       <c r="R58" t="n">
-        <v>6752417</v>
+        <v>6752545</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129309881</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129316313</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129307645</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129307362</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129306875</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129306675</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129306575</v>
+        <v>129307805</v>
       </c>
       <c r="B10" t="n">
-        <v>79663</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451153</v>
+        <v>451335</v>
       </c>
       <c r="R10" t="n">
-        <v>6752545</v>
+        <v>6752504</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129312692</v>
+        <v>129307040</v>
       </c>
       <c r="B11" t="n">
-        <v>79663</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,37 +1669,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451369</v>
+        <v>451262</v>
       </c>
       <c r="R11" t="n">
-        <v>6752313</v>
+        <v>6752514</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1723,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129307805</v>
+        <v>129306575</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>79689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,39 +1781,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451335</v>
+        <v>451153</v>
       </c>
       <c r="R12" t="n">
-        <v>6752504</v>
+        <v>6752545</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129307040</v>
+        <v>129312692</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>79689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,42 +1888,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451262</v>
+        <v>451369</v>
       </c>
       <c r="R13" t="n">
-        <v>6752514</v>
+        <v>6752313</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,7 +1987,7 @@
         <v>129307114</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,32 +2096,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129307042</v>
+        <v>129314017</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,13 +2131,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451262</v>
+        <v>451253</v>
       </c>
       <c r="R15" t="n">
-        <v>6752514</v>
+        <v>6752304</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129314017</v>
+        <v>129306457</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451253</v>
+        <v>451149</v>
       </c>
       <c r="R16" t="n">
-        <v>6752304</v>
+        <v>6752603</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129306457</v>
+        <v>129306554</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451149</v>
+        <v>451170</v>
       </c>
       <c r="R17" t="n">
-        <v>6752603</v>
+        <v>6752562</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129306554</v>
+        <v>129306100</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451170</v>
+        <v>451093</v>
       </c>
       <c r="R18" t="n">
-        <v>6752562</v>
+        <v>6752490</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2524,32 +2524,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129306100</v>
+        <v>129307042</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,13 +2559,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451093</v>
+        <v>451262</v>
       </c>
       <c r="R19" t="n">
-        <v>6752490</v>
+        <v>6752514</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2631,32 +2631,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129306511</v>
+        <v>129306556</v>
       </c>
       <c r="B20" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451170</v>
+        <v>451153</v>
       </c>
       <c r="R20" t="n">
-        <v>6752562</v>
+        <v>6752545</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129308438</v>
+        <v>129306511</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>79689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2749,39 +2749,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451260</v>
+        <v>451170</v>
       </c>
       <c r="R21" t="n">
-        <v>6752424</v>
+        <v>6752562</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2850,45 +2845,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129306556</v>
+        <v>129308438</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451153</v>
+        <v>451260</v>
       </c>
       <c r="R22" t="n">
-        <v>6752545</v>
+        <v>6752424</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2957,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129307237</v>
+        <v>129311305</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>79070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,42 +2968,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451256</v>
+        <v>451358</v>
       </c>
       <c r="R23" t="n">
-        <v>6752469</v>
+        <v>6752424</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3032,7 +3027,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3042,7 +3037,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,10 +3069,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129308406</v>
+        <v>129307012</v>
       </c>
       <c r="B24" t="n">
-        <v>79634</v>
+        <v>79070</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,21 +3080,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3104,13 +3104,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451275</v>
+        <v>451262</v>
       </c>
       <c r="R24" t="n">
-        <v>6752429</v>
+        <v>6752514</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3150,6 +3150,11 @@
       <c r="AB24" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3176,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129311305</v>
+        <v>129307237</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3187,37 +3192,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451358</v>
+        <v>451256</v>
       </c>
       <c r="R25" t="n">
-        <v>6752424</v>
+        <v>6752469</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3246,7 +3256,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3256,12 +3266,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3288,10 +3293,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129307012</v>
+        <v>129308406</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>79660</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3299,21 +3304,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3323,13 +3328,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451262</v>
+        <v>451275</v>
       </c>
       <c r="R26" t="n">
-        <v>6752514</v>
+        <v>6752429</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3369,11 +3374,6 @@
       <c r="AB26" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3403,7 +3403,7 @@
         <v>129306315</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>129308422</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>129306588</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>129306615</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>129313973</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>129314054</v>
       </c>
       <c r="B33" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>129309657</v>
       </c>
       <c r="B34" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>129311235</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>129310178</v>
       </c>
       <c r="B36" t="n">
-        <v>78447</v>
+        <v>78473</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>129307777</v>
       </c>
       <c r="B37" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>129310404</v>
       </c>
       <c r="B38" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>129307775</v>
       </c>
       <c r="B39" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>129306610</v>
       </c>
       <c r="B40" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>129307878</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>129313715</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>129310209</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>129310740</v>
       </c>
       <c r="B44" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>129306322</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>129306645</v>
       </c>
       <c r="B46" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>129310637</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,10 +5769,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129310466</v>
+        <v>129307334</v>
       </c>
       <c r="B49" t="n">
-        <v>79663</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5780,34 +5780,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>451463</v>
+        <v>451244</v>
       </c>
       <c r="R49" t="n">
-        <v>6752384</v>
+        <v>6752466</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5839,7 +5844,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5849,7 +5854,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5876,10 +5881,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129307334</v>
+        <v>129310466</v>
       </c>
       <c r="B50" t="n">
-        <v>57724</v>
+        <v>79689</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5887,39 +5892,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451244</v>
+        <v>451463</v>
       </c>
       <c r="R50" t="n">
-        <v>6752466</v>
+        <v>6752384</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5988,10 +5988,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129306533</v>
+        <v>129308051</v>
       </c>
       <c r="B51" t="n">
-        <v>57724</v>
+        <v>79070</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5999,42 +5999,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451170</v>
+        <v>451352</v>
       </c>
       <c r="R51" t="n">
-        <v>6752562</v>
+        <v>6752454</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6074,6 +6069,11 @@
       <c r="AB51" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129308051</v>
+        <v>129307728</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451352</v>
+        <v>451291</v>
       </c>
       <c r="R52" t="n">
-        <v>6752454</v>
+        <v>6752489</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6212,10 +6212,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129307728</v>
+        <v>129306533</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6223,37 +6223,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451291</v>
+        <v>451170</v>
       </c>
       <c r="R53" t="n">
-        <v>6752489</v>
+        <v>6752562</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6293,11 +6298,6 @@
       <c r="AB53" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6327,7 +6327,7 @@
         <v>129308409</v>
       </c>
       <c r="B54" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>129307246</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>129310742</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>129306555</v>
       </c>
       <c r="B58" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>129309688</v>
       </c>
       <c r="B59" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>129310867</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>129313806</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>129313901</v>
       </c>
       <c r="B62" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>129322141</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>129309515</v>
       </c>
       <c r="B64" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -1546,7 +1546,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129307805</v>
+        <v>129307040</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1577,7 +1577,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451335</v>
+        <v>451262</v>
       </c>
       <c r="R10" t="n">
-        <v>6752504</v>
+        <v>6752514</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129307040</v>
+        <v>129306575</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,42 +1669,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451262</v>
+        <v>451153</v>
       </c>
       <c r="R11" t="n">
-        <v>6752514</v>
+        <v>6752545</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1770,7 +1765,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129306575</v>
+        <v>129312692</v>
       </c>
       <c r="B12" t="n">
         <v>79689</v>
@@ -1805,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451153</v>
+        <v>451369</v>
       </c>
       <c r="R12" t="n">
-        <v>6752545</v>
+        <v>6752313</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1850,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129312692</v>
+        <v>129307805</v>
       </c>
       <c r="B13" t="n">
-        <v>79689</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,34 +1883,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451369</v>
+        <v>451335</v>
       </c>
       <c r="R13" t="n">
-        <v>6752313</v>
+        <v>6752504</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2957,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129311305</v>
+        <v>129307237</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,37 +2968,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451358</v>
+        <v>451256</v>
       </c>
       <c r="R23" t="n">
-        <v>6752424</v>
+        <v>6752469</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3027,7 +3032,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3037,12 +3042,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,7 +3069,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129307012</v>
+        <v>129311305</v>
       </c>
       <c r="B24" t="n">
         <v>79070</v>
@@ -3104,10 +3104,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451262</v>
+        <v>451358</v>
       </c>
       <c r="R24" t="n">
-        <v>6752514</v>
+        <v>6752424</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3181,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129307237</v>
+        <v>129307012</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,42 +3192,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451256</v>
+        <v>451262</v>
       </c>
       <c r="R25" t="n">
-        <v>6752469</v>
+        <v>6752514</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3267,6 +3262,11 @@
       <c r="AB25" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129306645</v>
+        <v>129310637</v>
       </c>
       <c r="B46" t="n">
-        <v>79689</v>
+        <v>79070</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451189</v>
+        <v>451442</v>
       </c>
       <c r="R46" t="n">
-        <v>6752531</v>
+        <v>6752403</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,7 +5523,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,10 +5555,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129310637</v>
+        <v>129306645</v>
       </c>
       <c r="B47" t="n">
-        <v>79070</v>
+        <v>79689</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5561,21 +5566,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5585,10 +5590,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451442</v>
+        <v>451189</v>
       </c>
       <c r="R47" t="n">
-        <v>6752403</v>
+        <v>6752531</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5620,7 +5625,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5630,12 +5635,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5662,32 +5662,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129307338</v>
+        <v>129310466</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>79689</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451244</v>
+        <v>451463</v>
       </c>
       <c r="R48" t="n">
-        <v>6752466</v>
+        <v>6752384</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5881,32 +5881,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129310466</v>
+        <v>129307338</v>
       </c>
       <c r="B50" t="n">
-        <v>79689</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451463</v>
+        <v>451244</v>
       </c>
       <c r="R50" t="n">
-        <v>6752384</v>
+        <v>6752466</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5988,10 +5988,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129308051</v>
+        <v>129308409</v>
       </c>
       <c r="B51" t="n">
-        <v>79070</v>
+        <v>79689</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5999,21 +5999,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6023,13 +6023,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451352</v>
+        <v>451275</v>
       </c>
       <c r="R51" t="n">
-        <v>6752454</v>
+        <v>6752429</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6069,11 +6069,6 @@
       <c r="AB51" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6100,7 +6095,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129307728</v>
+        <v>129308051</v>
       </c>
       <c r="B52" t="n">
         <v>79070</v>
@@ -6135,10 +6130,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451291</v>
+        <v>451352</v>
       </c>
       <c r="R52" t="n">
-        <v>6752489</v>
+        <v>6752454</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6212,10 +6207,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129306533</v>
+        <v>129307728</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6223,42 +6218,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451170</v>
+        <v>451291</v>
       </c>
       <c r="R53" t="n">
-        <v>6752562</v>
+        <v>6752489</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6298,6 +6288,11 @@
       <c r="AB53" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6324,10 +6319,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129308409</v>
+        <v>129306533</v>
       </c>
       <c r="B54" t="n">
-        <v>79689</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6335,34 +6330,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451275</v>
+        <v>451170</v>
       </c>
       <c r="R54" t="n">
-        <v>6752429</v>
+        <v>6752562</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6538,10 +6538,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129307246</v>
+        <v>129309688</v>
       </c>
       <c r="B56" t="n">
-        <v>79070</v>
+        <v>79660</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6549,21 +6549,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451256</v>
+        <v>451370</v>
       </c>
       <c r="R56" t="n">
-        <v>6752469</v>
+        <v>6752389</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6645,10 +6645,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129310742</v>
+        <v>129306555</v>
       </c>
       <c r="B57" t="n">
-        <v>79070</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6656,34 +6656,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451416</v>
+        <v>451153</v>
       </c>
       <c r="R57" t="n">
-        <v>6752417</v>
+        <v>6752545</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6715,7 +6720,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6725,7 +6730,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6752,10 +6757,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129306555</v>
+        <v>129307246</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6763,39 +6768,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451153</v>
+        <v>451256</v>
       </c>
       <c r="R58" t="n">
-        <v>6752545</v>
+        <v>6752469</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6864,10 +6864,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129309688</v>
+        <v>129310742</v>
       </c>
       <c r="B59" t="n">
-        <v>79660</v>
+        <v>79070</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6875,21 +6875,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451370</v>
+        <v>451416</v>
       </c>
       <c r="R59" t="n">
-        <v>6752389</v>
+        <v>6752417</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129309881</v>
+        <v>129306536</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451386</v>
+        <v>451170</v>
       </c>
       <c r="R2" t="n">
-        <v>6752391</v>
+        <v>6752562</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +785,7 @@
         <v>129316313</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129306536</v>
+        <v>129309881</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451170</v>
+        <v>451386</v>
       </c>
       <c r="R4" t="n">
-        <v>6752562</v>
+        <v>6752391</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129307645</v>
+        <v>129307362</v>
       </c>
       <c r="B6" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451237</v>
+        <v>451244</v>
       </c>
       <c r="R6" t="n">
-        <v>6752478</v>
+        <v>6752466</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,11 +1189,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129307362</v>
+        <v>129306675</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,13 +1250,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451244</v>
+        <v>451206</v>
       </c>
       <c r="R7" t="n">
-        <v>6752466</v>
+        <v>6752540</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,6 +1296,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129306875</v>
+        <v>129307645</v>
       </c>
       <c r="B8" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451243</v>
+        <v>451237</v>
       </c>
       <c r="R8" t="n">
-        <v>6752517</v>
+        <v>6752478</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1408,6 +1408,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129306675</v>
+        <v>129306875</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,13 +1474,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451206</v>
+        <v>451243</v>
       </c>
       <c r="R9" t="n">
-        <v>6752540</v>
+        <v>6752517</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1515,11 +1520,6 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129307040</v>
+        <v>129306575</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>79694</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,42 +1557,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451262</v>
+        <v>451153</v>
       </c>
       <c r="R10" t="n">
-        <v>6752514</v>
+        <v>6752545</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1658,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129306575</v>
+        <v>129312692</v>
       </c>
       <c r="B11" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451153</v>
+        <v>451369</v>
       </c>
       <c r="R11" t="n">
-        <v>6752545</v>
+        <v>6752313</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129312692</v>
+        <v>129307805</v>
       </c>
       <c r="B12" t="n">
-        <v>79689</v>
+        <v>57732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,34 +1771,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451369</v>
+        <v>451335</v>
       </c>
       <c r="R12" t="n">
-        <v>6752313</v>
+        <v>6752504</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129307805</v>
+        <v>129307040</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451335</v>
+        <v>451262</v>
       </c>
       <c r="R13" t="n">
-        <v>6752504</v>
+        <v>6752514</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>129307114</v>
       </c>
       <c r="B14" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>129314017</v>
       </c>
       <c r="B15" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129306457</v>
+        <v>129306100</v>
       </c>
       <c r="B16" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451149</v>
+        <v>451093</v>
       </c>
       <c r="R16" t="n">
-        <v>6752603</v>
+        <v>6752490</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2310,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129306554</v>
+        <v>129306457</v>
       </c>
       <c r="B17" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451170</v>
+        <v>451149</v>
       </c>
       <c r="R17" t="n">
-        <v>6752562</v>
+        <v>6752603</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129306100</v>
+        <v>129306554</v>
       </c>
       <c r="B18" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451093</v>
+        <v>451170</v>
       </c>
       <c r="R18" t="n">
-        <v>6752490</v>
+        <v>6752562</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2631,45 +2631,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129306556</v>
+        <v>129308438</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>57732</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451153</v>
+        <v>451260</v>
       </c>
       <c r="R20" t="n">
-        <v>6752545</v>
+        <v>6752424</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2741,7 +2746,7 @@
         <v>129306511</v>
       </c>
       <c r="B21" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,50 +2850,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129308438</v>
+        <v>129306556</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451260</v>
+        <v>451153</v>
       </c>
       <c r="R22" t="n">
-        <v>6752424</v>
+        <v>6752545</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2957,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129307237</v>
+        <v>129311305</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,42 +2968,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451256</v>
+        <v>451358</v>
       </c>
       <c r="R23" t="n">
-        <v>6752469</v>
+        <v>6752424</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3032,7 +3027,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3042,7 +3037,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,10 +3069,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129311305</v>
+        <v>129307012</v>
       </c>
       <c r="B24" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3104,10 +3104,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451358</v>
+        <v>451262</v>
       </c>
       <c r="R24" t="n">
-        <v>6752424</v>
+        <v>6752514</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3181,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129307012</v>
+        <v>129307237</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>57732</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,37 +3192,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451262</v>
+        <v>451256</v>
       </c>
       <c r="R25" t="n">
-        <v>6752514</v>
+        <v>6752469</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3262,11 +3267,6 @@
       <c r="AB25" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,7 +3296,7 @@
         <v>129308406</v>
       </c>
       <c r="B26" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>129306315</v>
       </c>
       <c r="B27" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129308422</v>
+        <v>129313973</v>
       </c>
       <c r="B29" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>451275</v>
+        <v>451258</v>
       </c>
       <c r="R29" t="n">
-        <v>6752429</v>
+        <v>6752314</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3721,10 +3721,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129306588</v>
+        <v>129314054</v>
       </c>
       <c r="B30" t="n">
-        <v>79070</v>
+        <v>78833</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3732,21 +3732,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>451153</v>
+        <v>451213</v>
       </c>
       <c r="R30" t="n">
-        <v>6752545</v>
+        <v>6752316</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3828,10 +3828,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129306615</v>
+        <v>129308422</v>
       </c>
       <c r="B31" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>451164</v>
+        <v>451275</v>
       </c>
       <c r="R31" t="n">
-        <v>6752537</v>
+        <v>6752429</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129313973</v>
+        <v>129306588</v>
       </c>
       <c r="B32" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>451258</v>
+        <v>451153</v>
       </c>
       <c r="R32" t="n">
-        <v>6752314</v>
+        <v>6752545</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4042,10 +4042,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129314054</v>
+        <v>129306615</v>
       </c>
       <c r="B33" t="n">
-        <v>78828</v>
+        <v>79075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4053,21 +4053,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>451213</v>
+        <v>451164</v>
       </c>
       <c r="R33" t="n">
-        <v>6752316</v>
+        <v>6752537</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4149,32 +4149,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129309657</v>
+        <v>129310404</v>
       </c>
       <c r="B34" t="n">
-        <v>92863</v>
+        <v>79665</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451370</v>
+        <v>451456</v>
       </c>
       <c r="R34" t="n">
-        <v>6752389</v>
+        <v>6752426</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4256,32 +4256,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129311235</v>
+        <v>129309657</v>
       </c>
       <c r="B35" t="n">
-        <v>79070</v>
+        <v>92869</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451357</v>
+        <v>451370</v>
       </c>
       <c r="R35" t="n">
-        <v>6752476</v>
+        <v>6752389</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4363,10 +4363,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129310178</v>
+        <v>129311235</v>
       </c>
       <c r="B36" t="n">
-        <v>78473</v>
+        <v>79075</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4374,21 +4374,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451435</v>
+        <v>451357</v>
       </c>
       <c r="R36" t="n">
-        <v>6752354</v>
+        <v>6752476</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4470,10 +4470,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129307777</v>
+        <v>129310178</v>
       </c>
       <c r="B37" t="n">
-        <v>79689</v>
+        <v>78478</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451291</v>
+        <v>451435</v>
       </c>
       <c r="R37" t="n">
-        <v>6752489</v>
+        <v>6752354</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4577,10 +4577,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129310404</v>
+        <v>129307777</v>
       </c>
       <c r="B38" t="n">
-        <v>79660</v>
+        <v>79694</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4612,13 +4612,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451456</v>
+        <v>451291</v>
       </c>
       <c r="R38" t="n">
-        <v>6752426</v>
+        <v>6752489</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4687,7 +4687,7 @@
         <v>129307775</v>
       </c>
       <c r="B39" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>129306610</v>
       </c>
       <c r="B40" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>129307878</v>
       </c>
       <c r="B41" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>129313715</v>
       </c>
       <c r="B42" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>129310209</v>
       </c>
       <c r="B43" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5229,10 +5229,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129310740</v>
+        <v>129306322</v>
       </c>
       <c r="B44" t="n">
-        <v>79689</v>
+        <v>79075</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5240,21 +5240,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>451416</v>
+        <v>451096</v>
       </c>
       <c r="R44" t="n">
-        <v>6752417</v>
+        <v>6752528</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5336,10 +5336,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129306322</v>
+        <v>129310740</v>
       </c>
       <c r="B45" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>451096</v>
+        <v>451416</v>
       </c>
       <c r="R45" t="n">
-        <v>6752528</v>
+        <v>6752417</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129310637</v>
+        <v>129306645</v>
       </c>
       <c r="B46" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451442</v>
+        <v>451189</v>
       </c>
       <c r="R46" t="n">
-        <v>6752403</v>
+        <v>6752531</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,12 +5523,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5555,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129306645</v>
+        <v>129310637</v>
       </c>
       <c r="B47" t="n">
-        <v>79689</v>
+        <v>79075</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5566,21 +5561,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5590,10 +5585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451189</v>
+        <v>451442</v>
       </c>
       <c r="R47" t="n">
-        <v>6752531</v>
+        <v>6752403</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5625,7 +5620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5635,7 +5630,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5665,7 +5665,7 @@
         <v>129310466</v>
       </c>
       <c r="B48" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>129307334</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5988,32 +5988,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129308409</v>
+        <v>129307240</v>
       </c>
       <c r="B51" t="n">
-        <v>79689</v>
+        <v>8450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6023,10 +6023,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451275</v>
+        <v>451256</v>
       </c>
       <c r="R51" t="n">
-        <v>6752429</v>
+        <v>6752469</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6098,7 +6098,7 @@
         <v>129308051</v>
       </c>
       <c r="B52" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>129307728</v>
       </c>
       <c r="B53" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6319,10 +6319,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129306533</v>
+        <v>129308409</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>79694</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6330,39 +6330,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451170</v>
+        <v>451275</v>
       </c>
       <c r="R54" t="n">
-        <v>6752562</v>
+        <v>6752429</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6431,45 +6426,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129307240</v>
+        <v>129306533</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>57732</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451256</v>
+        <v>451170</v>
       </c>
       <c r="R55" t="n">
-        <v>6752469</v>
+        <v>6752562</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6538,10 +6538,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129309688</v>
+        <v>129307246</v>
       </c>
       <c r="B56" t="n">
-        <v>79660</v>
+        <v>79075</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6549,21 +6549,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451370</v>
+        <v>451256</v>
       </c>
       <c r="R56" t="n">
-        <v>6752389</v>
+        <v>6752469</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6645,10 +6645,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129306555</v>
+        <v>129310742</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6656,39 +6656,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451153</v>
+        <v>451416</v>
       </c>
       <c r="R57" t="n">
-        <v>6752545</v>
+        <v>6752417</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6720,7 +6715,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6730,7 +6725,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6757,10 +6752,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129307246</v>
+        <v>129306555</v>
       </c>
       <c r="B58" t="n">
-        <v>79070</v>
+        <v>57732</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6768,34 +6763,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451256</v>
+        <v>451153</v>
       </c>
       <c r="R58" t="n">
-        <v>6752469</v>
+        <v>6752545</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6864,10 +6864,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129310742</v>
+        <v>129309688</v>
       </c>
       <c r="B59" t="n">
-        <v>79070</v>
+        <v>79665</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6875,21 +6875,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451416</v>
+        <v>451370</v>
       </c>
       <c r="R59" t="n">
-        <v>6752417</v>
+        <v>6752389</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6974,7 +6974,7 @@
         <v>129310867</v>
       </c>
       <c r="B60" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7083,35 +7083,39 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129313806</v>
+        <v>129313901</v>
       </c>
       <c r="B61" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -7168,7 +7172,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Bild på gran, garn</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7195,39 +7199,35 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129313901</v>
+        <v>129313806</v>
       </c>
       <c r="B62" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Bild på gran, garn</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7314,7 +7314,7 @@
         <v>129322141</v>
       </c>
       <c r="B63" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>129309515</v>
       </c>
       <c r="B64" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129306536</v>
+        <v>129309881</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451170</v>
+        <v>451386</v>
       </c>
       <c r="R2" t="n">
-        <v>6752562</v>
+        <v>6752391</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +790,7 @@
         <v>129316313</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129309881</v>
+        <v>129306536</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451386</v>
+        <v>451170</v>
       </c>
       <c r="R4" t="n">
-        <v>6752391</v>
+        <v>6752562</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,12 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129306869</v>
+        <v>129307645</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451243</v>
+        <v>451237</v>
       </c>
       <c r="R5" t="n">
-        <v>6752517</v>
+        <v>6752478</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,6 +1082,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,7 +1116,7 @@
         <v>129307362</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129306675</v>
+        <v>129306875</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451206</v>
+        <v>451243</v>
       </c>
       <c r="R7" t="n">
-        <v>6752540</v>
+        <v>6752517</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,11 +1301,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129307645</v>
+        <v>129306675</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451237</v>
+        <v>451206</v>
       </c>
       <c r="R8" t="n">
-        <v>6752478</v>
+        <v>6752540</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1439,32 +1439,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129306875</v>
+        <v>129306869</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129306575</v>
+        <v>129312692</v>
       </c>
       <c r="B10" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451153</v>
+        <v>451369</v>
       </c>
       <c r="R10" t="n">
-        <v>6752545</v>
+        <v>6752313</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129312692</v>
+        <v>129306575</v>
       </c>
       <c r="B11" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451369</v>
+        <v>451153</v>
       </c>
       <c r="R11" t="n">
-        <v>6752313</v>
+        <v>6752545</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129307805</v>
+        <v>129307040</v>
       </c>
       <c r="B12" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1800,13 +1800,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451335</v>
+        <v>451262</v>
       </c>
       <c r="R12" t="n">
-        <v>6752504</v>
+        <v>6752514</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129307040</v>
+        <v>129307805</v>
       </c>
       <c r="B13" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451262</v>
+        <v>451335</v>
       </c>
       <c r="R13" t="n">
-        <v>6752514</v>
+        <v>6752504</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>129307114</v>
       </c>
       <c r="B14" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,32 +2096,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129314017</v>
+        <v>129307042</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,13 +2131,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451253</v>
+        <v>451262</v>
       </c>
       <c r="R15" t="n">
-        <v>6752304</v>
+        <v>6752514</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129306100</v>
+        <v>129306457</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451093</v>
+        <v>451149</v>
       </c>
       <c r="R16" t="n">
-        <v>6752490</v>
+        <v>6752603</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2310,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129306457</v>
+        <v>129306554</v>
       </c>
       <c r="B17" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451149</v>
+        <v>451170</v>
       </c>
       <c r="R17" t="n">
-        <v>6752603</v>
+        <v>6752562</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129306554</v>
+        <v>129314017</v>
       </c>
       <c r="B18" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451170</v>
+        <v>451253</v>
       </c>
       <c r="R18" t="n">
-        <v>6752562</v>
+        <v>6752304</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2524,32 +2524,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129307042</v>
+        <v>129306100</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,13 +2559,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451262</v>
+        <v>451093</v>
       </c>
       <c r="R19" t="n">
-        <v>6752514</v>
+        <v>6752490</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>129308438</v>
       </c>
       <c r="B20" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2743,32 +2743,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129306511</v>
+        <v>129306556</v>
       </c>
       <c r="B21" t="n">
-        <v>79694</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451170</v>
+        <v>451153</v>
       </c>
       <c r="R21" t="n">
-        <v>6752562</v>
+        <v>6752545</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2850,32 +2850,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129306556</v>
+        <v>129306511</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79695</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451153</v>
+        <v>451170</v>
       </c>
       <c r="R22" t="n">
-        <v>6752545</v>
+        <v>6752562</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2957,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129311305</v>
+        <v>129307237</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,37 +2968,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451358</v>
+        <v>451256</v>
       </c>
       <c r="R23" t="n">
-        <v>6752424</v>
+        <v>6752469</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3027,7 +3032,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3037,12 +3042,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3072,7 +3072,7 @@
         <v>129307012</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3181,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129307237</v>
+        <v>129311305</v>
       </c>
       <c r="B25" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,42 +3192,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451256</v>
+        <v>451358</v>
       </c>
       <c r="R25" t="n">
-        <v>6752469</v>
+        <v>6752424</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3256,7 +3251,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3266,7 +3261,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,7 +3296,7 @@
         <v>129308406</v>
       </c>
       <c r="B26" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>129306315</v>
       </c>
       <c r="B27" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129313973</v>
+        <v>129308422</v>
       </c>
       <c r="B29" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>451258</v>
+        <v>451275</v>
       </c>
       <c r="R29" t="n">
-        <v>6752314</v>
+        <v>6752429</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3721,10 +3721,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129314054</v>
+        <v>129306588</v>
       </c>
       <c r="B30" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3732,21 +3732,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>451213</v>
+        <v>451153</v>
       </c>
       <c r="R30" t="n">
-        <v>6752316</v>
+        <v>6752545</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3828,10 +3828,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129308422</v>
+        <v>129306615</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>451275</v>
+        <v>451164</v>
       </c>
       <c r="R31" t="n">
-        <v>6752429</v>
+        <v>6752537</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129306588</v>
+        <v>129313973</v>
       </c>
       <c r="B32" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>451153</v>
+        <v>451258</v>
       </c>
       <c r="R32" t="n">
-        <v>6752545</v>
+        <v>6752314</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4042,10 +4042,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129306615</v>
+        <v>129314054</v>
       </c>
       <c r="B33" t="n">
-        <v>79075</v>
+        <v>78834</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4053,21 +4053,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>451164</v>
+        <v>451213</v>
       </c>
       <c r="R33" t="n">
-        <v>6752537</v>
+        <v>6752316</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4149,10 +4149,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129310404</v>
+        <v>129307777</v>
       </c>
       <c r="B34" t="n">
-        <v>79665</v>
+        <v>79695</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4184,13 +4184,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451456</v>
+        <v>451291</v>
       </c>
       <c r="R34" t="n">
-        <v>6752426</v>
+        <v>6752489</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4256,32 +4256,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129309657</v>
+        <v>129310178</v>
       </c>
       <c r="B35" t="n">
-        <v>92869</v>
+        <v>78479</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451370</v>
+        <v>451435</v>
       </c>
       <c r="R35" t="n">
-        <v>6752389</v>
+        <v>6752354</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4366,7 +4366,7 @@
         <v>129311235</v>
       </c>
       <c r="B36" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4470,10 +4470,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129310178</v>
+        <v>129310404</v>
       </c>
       <c r="B37" t="n">
-        <v>78478</v>
+        <v>79666</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451435</v>
+        <v>451456</v>
       </c>
       <c r="R37" t="n">
-        <v>6752354</v>
+        <v>6752426</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4577,32 +4577,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129307777</v>
+        <v>129309657</v>
       </c>
       <c r="B38" t="n">
-        <v>79694</v>
+        <v>92870</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4612,13 +4612,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451291</v>
+        <v>451370</v>
       </c>
       <c r="R38" t="n">
-        <v>6752489</v>
+        <v>6752389</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4687,7 +4687,7 @@
         <v>129307775</v>
       </c>
       <c r="B39" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>129306610</v>
       </c>
       <c r="B40" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129307878</v>
+        <v>129310209</v>
       </c>
       <c r="B41" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4933,13 +4933,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451297</v>
+        <v>451435</v>
       </c>
       <c r="R41" t="n">
-        <v>6752466</v>
+        <v>6752354</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5013,7 +5013,7 @@
         <v>129313715</v>
       </c>
       <c r="B42" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5117,10 +5117,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129310209</v>
+        <v>129307878</v>
       </c>
       <c r="B43" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5152,13 +5152,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>451435</v>
+        <v>451297</v>
       </c>
       <c r="R43" t="n">
-        <v>6752354</v>
+        <v>6752466</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5229,10 +5229,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129306322</v>
+        <v>129310740</v>
       </c>
       <c r="B44" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5240,21 +5240,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>451096</v>
+        <v>451416</v>
       </c>
       <c r="R44" t="n">
-        <v>6752528</v>
+        <v>6752417</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5336,10 +5336,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129310740</v>
+        <v>129306322</v>
       </c>
       <c r="B45" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>451416</v>
+        <v>451096</v>
       </c>
       <c r="R45" t="n">
-        <v>6752417</v>
+        <v>6752528</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5446,7 +5446,7 @@
         <v>129306645</v>
       </c>
       <c r="B46" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>129310637</v>
       </c>
       <c r="B47" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>129310466</v>
       </c>
       <c r="B48" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>129307334</v>
       </c>
       <c r="B49" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5988,32 +5988,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129307240</v>
+        <v>129308051</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6023,13 +6023,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451256</v>
+        <v>451352</v>
       </c>
       <c r="R51" t="n">
-        <v>6752469</v>
+        <v>6752454</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6069,6 +6069,11 @@
       <c r="AB51" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6095,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129308051</v>
+        <v>129306533</v>
       </c>
       <c r="B52" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6106,37 +6111,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451352</v>
+        <v>451170</v>
       </c>
       <c r="R52" t="n">
-        <v>6752454</v>
+        <v>6752562</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6176,11 +6186,6 @@
       <c r="AB52" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6207,10 +6212,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129307728</v>
+        <v>129308409</v>
       </c>
       <c r="B53" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6218,21 +6223,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6242,13 +6247,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451291</v>
+        <v>451275</v>
       </c>
       <c r="R53" t="n">
-        <v>6752489</v>
+        <v>6752429</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6288,11 +6293,6 @@
       <c r="AB53" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6319,10 +6319,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129308409</v>
+        <v>129307728</v>
       </c>
       <c r="B54" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6330,21 +6330,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6354,13 +6354,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451275</v>
+        <v>451291</v>
       </c>
       <c r="R54" t="n">
-        <v>6752429</v>
+        <v>6752489</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6400,6 +6400,11 @@
       <c r="AB54" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6426,50 +6431,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129306533</v>
+        <v>129307240</v>
       </c>
       <c r="B55" t="n">
-        <v>57732</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451170</v>
+        <v>451256</v>
       </c>
       <c r="R55" t="n">
-        <v>6752562</v>
+        <v>6752469</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6538,10 +6538,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129307246</v>
+        <v>129306555</v>
       </c>
       <c r="B56" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6549,34 +6549,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451256</v>
+        <v>451153</v>
       </c>
       <c r="R56" t="n">
-        <v>6752469</v>
+        <v>6752545</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6645,10 +6650,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129310742</v>
+        <v>129309688</v>
       </c>
       <c r="B57" t="n">
-        <v>79075</v>
+        <v>79666</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6656,21 +6661,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6680,10 +6685,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451416</v>
+        <v>451370</v>
       </c>
       <c r="R57" t="n">
-        <v>6752417</v>
+        <v>6752389</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6752,10 +6757,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129306555</v>
+        <v>129310742</v>
       </c>
       <c r="B58" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6763,39 +6768,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451153</v>
+        <v>451416</v>
       </c>
       <c r="R58" t="n">
-        <v>6752545</v>
+        <v>6752417</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6864,10 +6864,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129309688</v>
+        <v>129307246</v>
       </c>
       <c r="B59" t="n">
-        <v>79665</v>
+        <v>79076</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6875,21 +6875,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451370</v>
+        <v>451256</v>
       </c>
       <c r="R59" t="n">
-        <v>6752389</v>
+        <v>6752469</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6974,7 +6974,7 @@
         <v>129310867</v>
       </c>
       <c r="B60" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>129313901</v>
       </c>
       <c r="B61" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>129313806</v>
       </c>
       <c r="B62" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>129322141</v>
       </c>
       <c r="B63" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>129309515</v>
       </c>
       <c r="B64" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129309881</v>
+        <v>129316313</v>
       </c>
       <c r="B2" t="n">
         <v>79076</v>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451386</v>
+        <v>451213</v>
       </c>
       <c r="R2" t="n">
-        <v>6752391</v>
+        <v>6752316</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,11 +756,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129316313</v>
+        <v>129309881</v>
       </c>
       <c r="B3" t="n">
         <v>79076</v>
@@ -822,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451213</v>
+        <v>451386</v>
       </c>
       <c r="R3" t="n">
-        <v>6752316</v>
+        <v>6752391</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,6 +863,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129312692</v>
+        <v>129307040</v>
       </c>
       <c r="B10" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,37 +1557,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451369</v>
+        <v>451262</v>
       </c>
       <c r="R10" t="n">
-        <v>6752313</v>
+        <v>6752514</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1616,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129306575</v>
+        <v>129307805</v>
       </c>
       <c r="B11" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,34 +1669,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451153</v>
+        <v>451335</v>
       </c>
       <c r="R11" t="n">
-        <v>6752545</v>
+        <v>6752504</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129307040</v>
+        <v>129312692</v>
       </c>
       <c r="B12" t="n">
-        <v>57733</v>
+        <v>79695</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,42 +1781,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451262</v>
+        <v>451369</v>
       </c>
       <c r="R12" t="n">
-        <v>6752514</v>
+        <v>6752313</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1835,7 +1840,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1850,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129307805</v>
+        <v>129306575</v>
       </c>
       <c r="B13" t="n">
-        <v>57733</v>
+        <v>79695</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,39 +1888,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451335</v>
+        <v>451153</v>
       </c>
       <c r="R13" t="n">
-        <v>6752504</v>
+        <v>6752545</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2631,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129308438</v>
+        <v>129306511</v>
       </c>
       <c r="B20" t="n">
-        <v>57733</v>
+        <v>79695</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,39 +2642,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451260</v>
+        <v>451170</v>
       </c>
       <c r="R20" t="n">
-        <v>6752424</v>
+        <v>6752562</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2850,10 +2845,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129306511</v>
+        <v>129308438</v>
       </c>
       <c r="B22" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2861,34 +2856,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451170</v>
+        <v>451260</v>
       </c>
       <c r="R22" t="n">
-        <v>6752562</v>
+        <v>6752424</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3614,10 +3614,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129308422</v>
+        <v>129314054</v>
       </c>
       <c r="B29" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,21 +3625,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>451275</v>
+        <v>451213</v>
       </c>
       <c r="R29" t="n">
-        <v>6752429</v>
+        <v>6752316</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3721,7 +3721,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129306588</v>
+        <v>129308422</v>
       </c>
       <c r="B30" t="n">
         <v>79076</v>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>451153</v>
+        <v>451275</v>
       </c>
       <c r="R30" t="n">
-        <v>6752545</v>
+        <v>6752429</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129306615</v>
+        <v>129306588</v>
       </c>
       <c r="B31" t="n">
         <v>79076</v>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>451164</v>
+        <v>451153</v>
       </c>
       <c r="R31" t="n">
-        <v>6752537</v>
+        <v>6752545</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3935,7 +3935,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129313973</v>
+        <v>129306615</v>
       </c>
       <c r="B32" t="n">
         <v>79076</v>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>451258</v>
+        <v>451164</v>
       </c>
       <c r="R32" t="n">
-        <v>6752314</v>
+        <v>6752537</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4042,10 +4042,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129314054</v>
+        <v>129313973</v>
       </c>
       <c r="B33" t="n">
-        <v>78834</v>
+        <v>79076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4053,21 +4053,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>451213</v>
+        <v>451258</v>
       </c>
       <c r="R33" t="n">
-        <v>6752316</v>
+        <v>6752314</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4898,7 +4898,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129310209</v>
+        <v>129313715</v>
       </c>
       <c r="B41" t="n">
         <v>79076</v>
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451435</v>
+        <v>451335</v>
       </c>
       <c r="R41" t="n">
-        <v>6752354</v>
+        <v>6752312</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4979,11 +4979,6 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5010,7 +5005,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129313715</v>
+        <v>129307878</v>
       </c>
       <c r="B42" t="n">
         <v>79076</v>
@@ -5045,13 +5040,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451335</v>
+        <v>451297</v>
       </c>
       <c r="R42" t="n">
-        <v>6752312</v>
+        <v>6752466</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5080,7 +5075,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5090,7 +5085,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5117,7 +5117,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129307878</v>
+        <v>129310209</v>
       </c>
       <c r="B43" t="n">
         <v>79076</v>
@@ -5152,13 +5152,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>451297</v>
+        <v>451435</v>
       </c>
       <c r="R43" t="n">
-        <v>6752466</v>
+        <v>6752354</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6650,10 +6650,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129309688</v>
+        <v>129310742</v>
       </c>
       <c r="B57" t="n">
-        <v>79666</v>
+        <v>79076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6661,21 +6661,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6685,10 +6685,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451370</v>
+        <v>451416</v>
       </c>
       <c r="R57" t="n">
-        <v>6752389</v>
+        <v>6752417</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6757,7 +6757,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129310742</v>
+        <v>129307246</v>
       </c>
       <c r="B58" t="n">
         <v>79076</v>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451416</v>
+        <v>451256</v>
       </c>
       <c r="R58" t="n">
-        <v>6752417</v>
+        <v>6752469</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6864,10 +6864,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129307246</v>
+        <v>129309688</v>
       </c>
       <c r="B59" t="n">
-        <v>79076</v>
+        <v>79666</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6875,21 +6875,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451256</v>
+        <v>451370</v>
       </c>
       <c r="R59" t="n">
-        <v>6752469</v>
+        <v>6752389</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7083,39 +7083,35 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129313901</v>
+        <v>129313806</v>
       </c>
       <c r="B61" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -7172,7 +7168,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Bild på gran, garn</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7199,35 +7195,39 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129313806</v>
+        <v>129313901</v>
       </c>
       <c r="B62" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Bild på gran, garn</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 44318-2025 artfynd.xlsx
+++ b/artfynd/A 44318-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129316313</v>
+        <v>129309881</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451213</v>
+        <v>451386</v>
       </c>
       <c r="R2" t="n">
-        <v>6752316</v>
+        <v>6752391</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,6 +756,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129309881</v>
+        <v>129316313</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451386</v>
+        <v>451213</v>
       </c>
       <c r="R3" t="n">
-        <v>6752391</v>
+        <v>6752316</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,11 +868,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129307645</v>
+        <v>129306869</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451237</v>
+        <v>451243</v>
       </c>
       <c r="R5" t="n">
-        <v>6752478</v>
+        <v>6752517</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,11 +1082,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129307362</v>
+        <v>129307645</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451244</v>
+        <v>451237</v>
       </c>
       <c r="R6" t="n">
-        <v>6752466</v>
+        <v>6752478</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,6 +1189,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129306875</v>
+        <v>129307362</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451243</v>
+        <v>451244</v>
       </c>
       <c r="R7" t="n">
-        <v>6752517</v>
+        <v>6752466</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129306675</v>
+        <v>129306875</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451206</v>
+        <v>451243</v>
       </c>
       <c r="R8" t="n">
-        <v>6752540</v>
+        <v>6752517</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1408,11 +1408,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129306869</v>
+        <v>129306675</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,13 +1469,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451243</v>
+        <v>451206</v>
       </c>
       <c r="R9" t="n">
-        <v>6752517</v>
+        <v>6752540</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1520,6 +1515,11 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,7 +1546,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129307040</v>
+        <v>129307805</v>
       </c>
       <c r="B10" t="n">
         <v>57733</v>
@@ -1577,7 +1577,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451262</v>
+        <v>451335</v>
       </c>
       <c r="R10" t="n">
-        <v>6752514</v>
+        <v>6752504</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129307805</v>
+        <v>129307040</v>
       </c>
       <c r="B11" t="n">
         <v>57733</v>
@@ -1689,7 +1689,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1698,13 +1698,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451335</v>
+        <v>451262</v>
       </c>
       <c r="R11" t="n">
-        <v>6752504</v>
+        <v>6752514</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129312692</v>
+        <v>129306575</v>
       </c>
       <c r="B12" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451369</v>
+        <v>451153</v>
       </c>
       <c r="R12" t="n">
-        <v>6752313</v>
+        <v>6752545</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129306575</v>
+        <v>129312692</v>
       </c>
       <c r="B13" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451153</v>
+        <v>451369</v>
       </c>
       <c r="R13" t="n">
-        <v>6752545</v>
+        <v>6752313</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,32 +2096,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129307042</v>
+        <v>129314017</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,13 +2131,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451262</v>
+        <v>451253</v>
       </c>
       <c r="R15" t="n">
-        <v>6752514</v>
+        <v>6752304</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2206,7 +2206,7 @@
         <v>129306457</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>129306554</v>
       </c>
       <c r="B17" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129314017</v>
+        <v>129306100</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451253</v>
+        <v>451093</v>
       </c>
       <c r="R18" t="n">
-        <v>6752304</v>
+        <v>6752490</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2524,32 +2524,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129306100</v>
+        <v>129307042</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,13 +2559,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451093</v>
+        <v>451262</v>
       </c>
       <c r="R19" t="n">
-        <v>6752490</v>
+        <v>6752514</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2631,32 +2631,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129306511</v>
+        <v>129306556</v>
       </c>
       <c r="B20" t="n">
-        <v>79695</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451170</v>
+        <v>451153</v>
       </c>
       <c r="R20" t="n">
-        <v>6752562</v>
+        <v>6752545</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,32 +2738,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129306556</v>
+        <v>129306511</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451153</v>
+        <v>451170</v>
       </c>
       <c r="R21" t="n">
-        <v>6752545</v>
+        <v>6752562</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129307237</v>
+        <v>129311305</v>
       </c>
       <c r="B23" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,42 +2968,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451256</v>
+        <v>451358</v>
       </c>
       <c r="R23" t="n">
-        <v>6752469</v>
+        <v>6752424</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3032,7 +3027,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3042,7 +3037,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3072,7 +3072,7 @@
         <v>129307012</v>
       </c>
       <c r="B24" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3181,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129311305</v>
+        <v>129307237</v>
       </c>
       <c r="B25" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,37 +3192,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451358</v>
+        <v>451256</v>
       </c>
       <c r="R25" t="n">
-        <v>6752424</v>
+        <v>6752469</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3251,7 +3256,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3261,12 +3266,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,7 +3296,7 @@
         <v>129308406</v>
       </c>
       <c r="B26" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>129306315</v>
       </c>
       <c r="B27" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129314054</v>
+        <v>129308422</v>
       </c>
       <c r="B29" t="n">
-        <v>78834</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,21 +3625,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>451213</v>
+        <v>451275</v>
       </c>
       <c r="R29" t="n">
-        <v>6752316</v>
+        <v>6752429</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3721,10 +3721,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129308422</v>
+        <v>129306588</v>
       </c>
       <c r="B30" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>451275</v>
+        <v>451153</v>
       </c>
       <c r="R30" t="n">
-        <v>6752429</v>
+        <v>6752545</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3828,10 +3828,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129306588</v>
+        <v>129306615</v>
       </c>
       <c r="B31" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>451153</v>
+        <v>451164</v>
       </c>
       <c r="R31" t="n">
-        <v>6752545</v>
+        <v>6752537</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129306615</v>
+        <v>129313973</v>
       </c>
       <c r="B32" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>451164</v>
+        <v>451258</v>
       </c>
       <c r="R32" t="n">
-        <v>6752537</v>
+        <v>6752314</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4042,10 +4042,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129313973</v>
+        <v>129314054</v>
       </c>
       <c r="B33" t="n">
-        <v>79076</v>
+        <v>78839</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4053,21 +4053,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>451258</v>
+        <v>451213</v>
       </c>
       <c r="R33" t="n">
-        <v>6752314</v>
+        <v>6752316</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129307777</v>
+        <v>129310178</v>
       </c>
       <c r="B34" t="n">
-        <v>79695</v>
+        <v>78484</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4184,13 +4184,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451291</v>
+        <v>451435</v>
       </c>
       <c r="R34" t="n">
-        <v>6752489</v>
+        <v>6752354</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4256,10 +4256,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129310178</v>
+        <v>129307777</v>
       </c>
       <c r="B35" t="n">
-        <v>78479</v>
+        <v>79700</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451435</v>
+        <v>451291</v>
       </c>
       <c r="R35" t="n">
-        <v>6752354</v>
+        <v>6752489</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4366,7 +4366,7 @@
         <v>129311235</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4470,32 +4470,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129310404</v>
+        <v>129309657</v>
       </c>
       <c r="B37" t="n">
-        <v>79666</v>
+        <v>92875</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451456</v>
+        <v>451370</v>
       </c>
       <c r="R37" t="n">
-        <v>6752426</v>
+        <v>6752389</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4577,32 +4577,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129309657</v>
+        <v>129310404</v>
       </c>
       <c r="B38" t="n">
-        <v>92870</v>
+        <v>79671</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451370</v>
+        <v>451456</v>
       </c>
       <c r="R38" t="n">
-        <v>6752389</v>
+        <v>6752426</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4687,7 +4687,7 @@
         <v>129307775</v>
       </c>
       <c r="B39" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>129306610</v>
       </c>
       <c r="B40" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129313715</v>
+        <v>129307878</v>
       </c>
       <c r="B41" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4933,13 +4933,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451335</v>
+        <v>451297</v>
       </c>
       <c r="R41" t="n">
-        <v>6752312</v>
+        <v>6752466</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4978,7 +4978,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5005,10 +5010,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129307878</v>
+        <v>129313715</v>
       </c>
       <c r="B42" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5040,13 +5045,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451297</v>
+        <v>451335</v>
       </c>
       <c r="R42" t="n">
-        <v>6752466</v>
+        <v>6752312</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5075,7 +5080,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5085,12 +5090,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5120,7 +5120,7 @@
         <v>129310209</v>
       </c>
       <c r="B43" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>129310740</v>
       </c>
       <c r="B44" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>129306322</v>
       </c>
       <c r="B45" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>129306645</v>
       </c>
       <c r="B46" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>129310637</v>
       </c>
       <c r="B47" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5662,10 +5662,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129310466</v>
+        <v>129307334</v>
       </c>
       <c r="B48" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5673,34 +5673,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451463</v>
+        <v>451244</v>
       </c>
       <c r="R48" t="n">
-        <v>6752384</v>
+        <v>6752466</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5732,7 +5737,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5742,7 +5747,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5769,40 +5774,35 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129307334</v>
+        <v>129307338</v>
       </c>
       <c r="B49" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
@@ -5881,32 +5881,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129307338</v>
+        <v>129310466</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451244</v>
+        <v>451463</v>
       </c>
       <c r="R50" t="n">
-        <v>6752466</v>
+        <v>6752384</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5988,10 +5988,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129308051</v>
+        <v>129308409</v>
       </c>
       <c r="B51" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5999,21 +5999,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6023,13 +6023,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451352</v>
+        <v>451275</v>
       </c>
       <c r="R51" t="n">
-        <v>6752454</v>
+        <v>6752429</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6069,11 +6069,6 @@
       <c r="AB51" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6100,10 +6095,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129306533</v>
+        <v>129308051</v>
       </c>
       <c r="B52" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6111,42 +6106,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451170</v>
+        <v>451352</v>
       </c>
       <c r="R52" t="n">
-        <v>6752562</v>
+        <v>6752454</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6186,6 +6176,11 @@
       <c r="AB52" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6212,10 +6207,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129308409</v>
+        <v>129307728</v>
       </c>
       <c r="B53" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6223,21 +6218,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6247,13 +6242,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451275</v>
+        <v>451291</v>
       </c>
       <c r="R53" t="n">
-        <v>6752429</v>
+        <v>6752489</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6293,6 +6288,11 @@
       <c r="AB53" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6319,10 +6319,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129307728</v>
+        <v>129306533</v>
       </c>
       <c r="B54" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6330,37 +6330,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sundsmor, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451291</v>
+        <v>451170</v>
       </c>
       <c r="R54" t="n">
-        <v>6752489</v>
+        <v>6752562</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6400,11 +6405,6 @@
       <c r="AB54" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6650,10 +6650,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129310742</v>
+        <v>129307246</v>
       </c>
       <c r="B57" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6685,10 +6685,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451416</v>
+        <v>451256</v>
       </c>
       <c r="R57" t="n">
-        <v>6752417</v>
+        <v>6752469</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6720,7 +6720,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6757,10 +6757,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129307246</v>
+        <v>129310742</v>
       </c>
       <c r="B58" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451256</v>
+        <v>451416</v>
       </c>
       <c r="R58" t="n">
-        <v>6752469</v>
+        <v>6752417</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6867,7 +6867,7 @@
         <v>129309688</v>
       </c>
       <c r="B59" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>129310867</v>
       </c>
       <c r="B60" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>129313806</v>
       </c>
       <c r="B61" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>129313901</v>
       </c>
       <c r="B62" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>129322141</v>
       </c>
       <c r="B63" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>129309515</v>
       </c>
       <c r="B64" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
